--- a/public/downloads/ZhangDopant-dependent2025.xlsx
+++ b/public/downloads/ZhangDopant-dependent2025.xlsx
@@ -8,30 +8,32 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="Allegro-OAM-L" sheetId="3" r:id="rId3"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="4" r:id="rId4"/>
-    <sheet name="CHGNetv0.3.0" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="NequIP-OAM-L" sheetId="12" r:id="rId12"/>
-    <sheet name="ORB-v3" sheetId="13" r:id="rId13"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="17" r:id="rId17"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="18" r:id="rId18"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="Allegro-OAM-L" sheetId="5" r:id="rId5"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="6" r:id="rId6"/>
+    <sheet name="CHGNetv0.3.0" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="NequIP-OAM-L" sheetId="14" r:id="rId14"/>
+    <sheet name="ORB-v3" sheetId="15" r:id="rId15"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="19" r:id="rId19"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="20" r:id="rId20"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="59">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -63,10 +65,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -169,6 +171,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>B</t>
@@ -660,7 +683,7 @@
         <v>0.6311392135106113</v>
       </c>
       <c r="J3" s="4">
-        <v>6.833655091462846</v>
+        <v>6.833655091462845</v>
       </c>
       <c r="K3" s="4">
         <v>88.95262190949883</v>
@@ -672,10 +695,10 @@
         <v>8272</v>
       </c>
       <c r="N3" s="5">
-        <v>157216.3116247654</v>
+        <v>157216311.6247654</v>
       </c>
       <c r="O3" s="4">
-        <v>0.064512153503613</v>
+        <v>64.51215350361301</v>
       </c>
       <c r="P3" s="5">
         <v>2437003</v>
@@ -722,10 +745,10 @@
         <v>8272</v>
       </c>
       <c r="N4" s="5">
-        <v>82298.46655201912</v>
+        <v>82298466.55201912</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04656465623102108</v>
+        <v>46.56465623102108</v>
       </c>
       <c r="P4" s="5">
         <v>1767402</v>
@@ -772,10 +795,10 @@
         <v>8272</v>
       </c>
       <c r="N5" s="5">
-        <v>165573.3744380474</v>
+        <v>165573374.4380474</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1181300027382938</v>
+        <v>118.1300027382938</v>
       </c>
       <c r="P5" s="5">
         <v>1401620</v>
@@ -822,10 +845,10 @@
         <v>8272</v>
       </c>
       <c r="N6" s="5">
-        <v>238741.4978296757</v>
+        <v>238741497.8296757</v>
       </c>
       <c r="O6" s="4">
-        <v>0.1113509734309101</v>
+        <v>111.3509734309101</v>
       </c>
       <c r="P6" s="5">
         <v>2144045</v>
@@ -872,10 +895,10 @@
         <v>8272</v>
       </c>
       <c r="N7" s="5">
-        <v>226840.2322740555</v>
+        <v>226840232.2740555</v>
       </c>
       <c r="O7" s="4">
-        <v>0.399779758789551</v>
+        <v>399.779758789551</v>
       </c>
       <c r="P7" s="5">
         <v>567413</v>
@@ -904,13 +927,13 @@
         <v>5.560928433268859</v>
       </c>
       <c r="H8" s="4">
-        <v>0.8645036786241207</v>
+        <v>0.8645036786241208</v>
       </c>
       <c r="I8" s="4">
         <v>0.7695060854669614</v>
       </c>
       <c r="J8" s="4">
-        <v>1.040229314158726</v>
+        <v>1.040229314158725</v>
       </c>
       <c r="K8" s="4">
         <v>91.05157222463453</v>
@@ -922,10 +945,10 @@
         <v>8272</v>
       </c>
       <c r="N8" s="5">
-        <v>30020.93371582031</v>
+        <v>30020933.71582031</v>
       </c>
       <c r="O8" s="4">
-        <v>0.03004322578935601</v>
+        <v>30.04322578935601</v>
       </c>
       <c r="P8" s="5">
         <v>999258</v>
@@ -972,10 +995,10 @@
         <v>8272</v>
       </c>
       <c r="N9" s="5">
-        <v>63685.52204585075</v>
+        <v>63685522.04585075</v>
       </c>
       <c r="O9" s="4">
-        <v>0.04262800985409523</v>
+        <v>42.62800985409523</v>
       </c>
       <c r="P9" s="5">
         <v>1493983</v>
@@ -1004,13 +1027,13 @@
         <v>6.914893617021277</v>
       </c>
       <c r="H10" s="4">
-        <v>0.7861784532342906</v>
+        <v>0.7861784532342905</v>
       </c>
       <c r="I10" s="4">
         <v>0.5702129720588882</v>
       </c>
       <c r="J10" s="4">
-        <v>0.8867055291225574</v>
+        <v>0.8867055291225573</v>
       </c>
       <c r="K10" s="4">
         <v>89.24772447663777</v>
@@ -1022,10 +1045,10 @@
         <v>8272</v>
       </c>
       <c r="N10" s="5">
-        <v>99576.1155025959</v>
+        <v>99576115.5025959</v>
       </c>
       <c r="O10" s="4">
-        <v>0.09739600336331154</v>
+        <v>97.39600336331154</v>
       </c>
       <c r="P10" s="5">
         <v>1022384</v>
@@ -1072,10 +1095,10 @@
         <v>8272</v>
       </c>
       <c r="N11" s="5">
-        <v>79503.38049173355</v>
+        <v>79503380.49173355</v>
       </c>
       <c r="O11" s="4">
-        <v>0.06508742670135684</v>
+        <v>65.08742670135683</v>
       </c>
       <c r="P11" s="5">
         <v>1221486</v>
@@ -1104,7 +1127,7 @@
         <v>4.073984526112186</v>
       </c>
       <c r="H12" s="4">
-        <v>0.7463639403687355</v>
+        <v>0.7463639403687357</v>
       </c>
       <c r="I12" s="4">
         <v>0.4097561094678731</v>
@@ -1122,10 +1145,10 @@
         <v>8272</v>
       </c>
       <c r="N12" s="5">
-        <v>69215.84616398811</v>
+        <v>69215846.16398811</v>
       </c>
       <c r="O12" s="4">
-        <v>0.05944688079591466</v>
+        <v>59.44688079591466</v>
       </c>
       <c r="P12" s="5">
         <v>1164331</v>
@@ -1172,10 +1195,10 @@
         <v>8272</v>
       </c>
       <c r="N13" s="5">
-        <v>43666.44592142105</v>
+        <v>43666445.92142105</v>
       </c>
       <c r="O13" s="4">
-        <v>0.03787517947844838</v>
+        <v>37.87517947844838</v>
       </c>
       <c r="P13" s="5">
         <v>1152904</v>
@@ -1204,7 +1227,7 @@
         <v>21.1073500967118</v>
       </c>
       <c r="H14" s="4">
-        <v>2.024135796006233</v>
+        <v>2.024135796006232</v>
       </c>
       <c r="I14" s="4">
         <v>0.5775122909569226</v>
@@ -1222,10 +1245,10 @@
         <v>8272</v>
       </c>
       <c r="N14" s="5">
-        <v>126510.4710562229</v>
+        <v>126510471.0562229</v>
       </c>
       <c r="O14" s="4">
-        <v>0.07673947379653222</v>
+        <v>76.73947379653222</v>
       </c>
       <c r="P14" s="5">
         <v>1648571</v>
@@ -1272,10 +1295,10 @@
         <v>8272</v>
       </c>
       <c r="N15" s="5">
-        <v>387370.4859704971</v>
+        <v>387370485.9704971</v>
       </c>
       <c r="O15" s="4">
-        <v>0.5402875234430641</v>
+        <v>540.2875234430641</v>
       </c>
       <c r="P15" s="5">
         <v>716971</v>
@@ -1322,10 +1345,10 @@
         <v>8272</v>
       </c>
       <c r="N16" s="5">
-        <v>466421.2412323952</v>
+        <v>466421241.2323952</v>
       </c>
       <c r="O16" s="4">
-        <v>0.5333460350574375</v>
+        <v>533.3460350574375</v>
       </c>
       <c r="P16" s="5">
         <v>874519</v>
@@ -1372,10 +1395,10 @@
         <v>8272</v>
       </c>
       <c r="N17" s="5">
-        <v>128505.6936891079</v>
+        <v>128505693.6891079</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1312836558468267</v>
+        <v>131.2836558468267</v>
       </c>
       <c r="P17" s="5">
         <v>978840</v>
@@ -1422,10 +1445,10 @@
         <v>8272</v>
       </c>
       <c r="N18" s="5">
-        <v>175359.670337677</v>
+        <v>175359670.337677</v>
       </c>
       <c r="O18" s="4">
-        <v>0.1097824445030901</v>
+        <v>109.7824445030901</v>
       </c>
       <c r="P18" s="5">
         <v>1597338</v>
@@ -1453,7 +1476,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1464,9 +1487,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1500,8 +1529,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1523,255 +1560,381 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>1.359211988369509</v>
+        <v>0.9688806581149634</v>
       </c>
       <c r="C3" s="4">
-        <v>1.040747269022134</v>
+        <v>0.9077242341395307</v>
       </c>
       <c r="D3" s="4">
-        <v>1.592577659728225</v>
+        <v>1.433518686758558</v>
       </c>
       <c r="E3" s="4">
-        <v>88.96370582617</v>
+        <v>89.28797536206457</v>
       </c>
       <c r="F3" s="4">
-        <v>82.71742210085675</v>
+        <v>82.00563130196262</v>
       </c>
       <c r="G3" s="5">
         <v>3490</v>
       </c>
       <c r="H3" s="5">
-        <v>1971</v>
+        <v>1948</v>
       </c>
       <c r="I3" s="5">
-        <v>507</v>
+        <v>951</v>
       </c>
       <c r="J3" s="5">
-        <v>1012</v>
+        <v>591</v>
       </c>
       <c r="K3" s="5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L3" s="5">
-        <v>429</v>
+        <v>397</v>
       </c>
       <c r="M3" s="5">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>186</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.9819113485465572</v>
+      </c>
+      <c r="O3" s="5">
+        <v>2134</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6577432386678714</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5850542866169058</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2116</v>
+      </c>
+      <c r="S3" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7773259941232461</v>
+        <v>1.626381551450666</v>
       </c>
       <c r="C4" s="4">
-        <v>0.7795331661404522</v>
+        <v>1.573717270044479</v>
       </c>
       <c r="D4" s="4">
-        <v>0.8007050363370546</v>
+        <v>1.859486304924868</v>
       </c>
       <c r="E4" s="4">
-        <v>89.63194662480382</v>
+        <v>92.19374672946101</v>
       </c>
       <c r="F4" s="4">
-        <v>88.70069695405009</v>
+        <v>85.37032352435013</v>
       </c>
       <c r="G4" s="5">
         <v>1300</v>
       </c>
       <c r="H4" s="5">
-        <v>1282</v>
+        <v>772</v>
       </c>
       <c r="I4" s="5">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="J4" s="5">
-        <v>14</v>
+        <v>497</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="5">
-        <v>14</v>
+        <v>220</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>274</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1.725644560536028</v>
+      </c>
+      <c r="O4" s="5">
+        <v>1046</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3428987287192891</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2982080429397095</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1046</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1367257280337732</v>
+        <v>0.379929596218835</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1187081056841091</v>
+        <v>0.4095374063859065</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1360975668276147</v>
+        <v>0.3320893475605322</v>
       </c>
       <c r="E5" s="4">
-        <v>89.12671417773461</v>
+        <v>92.14947089947093</v>
       </c>
       <c r="F5" s="4">
-        <v>86.90205425943722</v>
+        <v>82.3759720890594</v>
       </c>
       <c r="G5" s="5">
         <v>1260</v>
       </c>
       <c r="H5" s="5">
-        <v>1158</v>
+        <v>1027</v>
       </c>
       <c r="I5" s="5">
-        <v>63</v>
+        <v>206</v>
       </c>
       <c r="J5" s="5">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="K5" s="5">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L5" s="5">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.3360989651063747</v>
+      </c>
+      <c r="O5" s="5">
+        <v>1027</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3077647989374864</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3027406284166927</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1027</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
-        <v>0.2758669290680116</v>
+        <v>0.641312479962494</v>
       </c>
       <c r="C6" s="4">
-        <v>0.2732306190922615</v>
+        <v>0.6348324158098404</v>
       </c>
       <c r="D6" s="4">
-        <v>0.2812357022797321</v>
+        <v>0.4643216367702424</v>
       </c>
       <c r="E6" s="4">
-        <v>89.86605676753472</v>
+        <v>92.75158339197748</v>
       </c>
       <c r="F6" s="4">
-        <v>88.84360983458363</v>
+        <v>88.02086157304802</v>
       </c>
       <c r="G6" s="5">
         <v>1015</v>
       </c>
       <c r="H6" s="5">
-        <v>1008</v>
+        <v>976</v>
       </c>
       <c r="I6" s="5">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J6" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.6346994263359634</v>
+      </c>
+      <c r="O6" s="5">
+        <v>976</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1767370994514929</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1727991608346863</v>
+      </c>
+      <c r="R6" s="5">
+        <v>976</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
-        <v>0.1904512549905687</v>
+        <v>0.5922682712079942</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1719305890793098</v>
+        <v>0.5314704069337181</v>
       </c>
       <c r="D7" s="4">
-        <v>0.1458937164910269</v>
+        <v>0.2607375434064936</v>
       </c>
       <c r="E7" s="4">
-        <v>88.82858973185687</v>
+        <v>91.31402336719439</v>
       </c>
       <c r="F7" s="4">
-        <v>84.55605046765972</v>
+        <v>82.70086576178083</v>
       </c>
       <c r="G7" s="5">
         <v>669</v>
       </c>
       <c r="H7" s="5">
-        <v>608</v>
+        <v>499</v>
       </c>
       <c r="I7" s="5">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J7" s="5">
-        <v>57</v>
+        <v>157</v>
       </c>
       <c r="K7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>56</v>
+        <v>157</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.5273995345712378</v>
+      </c>
+      <c r="O7" s="5">
+        <v>499</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2482929496641412</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.2334397182719874</v>
+      </c>
+      <c r="R7" s="5">
+        <v>499</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
-        <v>0.3148760101653681</v>
+        <v>0.2409181859402017</v>
       </c>
       <c r="C8" s="4">
-        <v>0.3145416642316777</v>
+        <v>0.1871982201257406</v>
       </c>
       <c r="D8" s="4">
-        <v>0.3369432878492517</v>
+        <v>0.2236282857700216</v>
       </c>
       <c r="E8" s="4">
-        <v>89.79977492855878</v>
+        <v>93.62719065321296</v>
       </c>
       <c r="F8" s="4">
-        <v>88.23318197317087</v>
+        <v>87.8298944637108</v>
       </c>
       <c r="G8" s="5">
         <v>538</v>
       </c>
       <c r="H8" s="5">
-        <v>514</v>
+        <v>464</v>
       </c>
       <c r="I8" s="5">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="J8" s="5">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K8" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>0.05761231017444256</v>
+      </c>
+      <c r="O8" s="5">
+        <v>464</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.2291088766084902</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1704692913477198</v>
+      </c>
+      <c r="R8" s="5">
+        <v>464</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1782,6 +1945,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1789,7 +1953,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1800,9 +1964,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1836,8 +2006,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1859,255 +2037,381 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.803182596080712</v>
+        <v>2.728989691339296</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5780735837606271</v>
+        <v>1.11393331567318</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7814287548181286</v>
+        <v>3.758038630237912</v>
       </c>
       <c r="E3" s="4">
-        <v>88.47026489678967</v>
+        <v>75.12162056799801</v>
       </c>
       <c r="F3" s="4">
-        <v>77.59973526150158</v>
+        <v>64.97866066678203</v>
       </c>
       <c r="G3" s="5">
         <v>3490</v>
       </c>
       <c r="H3" s="5">
-        <v>1665</v>
+        <v>430</v>
       </c>
       <c r="I3" s="5">
-        <v>909</v>
+        <v>541</v>
       </c>
       <c r="J3" s="5">
-        <v>916</v>
+        <v>2519</v>
       </c>
       <c r="K3" s="5">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L3" s="5">
-        <v>863</v>
+        <v>1941</v>
       </c>
       <c r="M3" s="5">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>539</v>
+      </c>
+      <c r="N3" s="4">
+        <v>2.260122762536059</v>
+      </c>
+      <c r="O3" s="5">
+        <v>969</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.303721110663094</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.8798321082706825</v>
+      </c>
+      <c r="R3" s="5">
+        <v>830</v>
+      </c>
+      <c r="S3" s="5">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>2.479684247662037</v>
+        <v>0.2451883431170309</v>
       </c>
       <c r="C4" s="4">
-        <v>1.733694535083582</v>
+        <v>0.2349038390628152</v>
       </c>
       <c r="D4" s="4">
-        <v>7.970300430476597</v>
+        <v>0.3363890841250518</v>
       </c>
       <c r="E4" s="4">
-        <v>83.64358974358983</v>
+        <v>83.08087388801675</v>
       </c>
       <c r="F4" s="4">
-        <v>61.00218551023918</v>
+        <v>74.266399931165</v>
       </c>
       <c r="G4" s="5">
         <v>1300</v>
       </c>
       <c r="H4" s="5">
-        <v>205</v>
+        <v>787</v>
       </c>
       <c r="I4" s="5">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="J4" s="5">
-        <v>985</v>
+        <v>479</v>
       </c>
       <c r="K4" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>845</v>
+        <v>479</v>
       </c>
       <c r="M4" s="5">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.1123956590570702</v>
+      </c>
+      <c r="O4" s="5">
+        <v>787</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2323634538590199</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2025924505005597</v>
+      </c>
+      <c r="R4" s="5">
+        <v>787</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2926986232194212</v>
+        <v>0.9793543063116789</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1950118682450668</v>
+        <v>0.9298872780254815</v>
       </c>
       <c r="D5" s="4">
-        <v>0.622406754775047</v>
+        <v>0.8240731488270691</v>
       </c>
       <c r="E5" s="4">
-        <v>89.88483965014582</v>
+        <v>83.52000323939099</v>
       </c>
       <c r="F5" s="4">
-        <v>78.13611910088407</v>
+        <v>75.89057561876398</v>
       </c>
       <c r="G5" s="5">
         <v>1260</v>
       </c>
       <c r="H5" s="5">
-        <v>880</v>
+        <v>842</v>
       </c>
       <c r="I5" s="5">
-        <v>344</v>
+        <v>10</v>
       </c>
       <c r="J5" s="5">
-        <v>36</v>
+        <v>408</v>
       </c>
       <c r="K5" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L5" s="5">
-        <v>27</v>
+        <v>403</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+        <v>2</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.9325342989873711</v>
+      </c>
+      <c r="O5" s="5">
+        <v>844</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3251050665335309</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3124280655756538</v>
+      </c>
+      <c r="R5" s="5">
+        <v>844</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
-        <v>0.182127381600939</v>
+        <v>1.344256027209443</v>
       </c>
       <c r="C6" s="4">
-        <v>0.1776947214626322</v>
+        <v>1.374319954966815</v>
       </c>
       <c r="D6" s="4">
-        <v>0.207890135351507</v>
+        <v>1.297535525345494</v>
       </c>
       <c r="E6" s="4">
-        <v>90.65822190945345</v>
+        <v>83.35059146811423</v>
       </c>
       <c r="F6" s="4">
-        <v>84.37246669091054</v>
+        <v>77.69055884330241</v>
       </c>
       <c r="G6" s="5">
         <v>1015</v>
       </c>
       <c r="H6" s="5">
-        <v>811</v>
+        <v>696</v>
       </c>
       <c r="I6" s="5">
-        <v>203</v>
+        <v>18</v>
       </c>
       <c r="J6" s="5">
-        <v>1</v>
+        <v>301</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>1</v>
+        <v>301</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-1.374319954966815</v>
+      </c>
+      <c r="O6" s="5">
+        <v>696</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1689538796812292</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1544345146716327</v>
+      </c>
+      <c r="R6" s="5">
+        <v>696</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
-        <v>0.2016252396962697</v>
+        <v>1.288931432471761</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1921791241875918</v>
+        <v>1.238176652071127</v>
       </c>
       <c r="D7" s="4">
-        <v>0.2748809197757763</v>
+        <v>0.8988287586669055</v>
       </c>
       <c r="E7" s="4">
-        <v>90.96341376610434</v>
+        <v>81.81182188869568</v>
       </c>
       <c r="F7" s="4">
-        <v>85.09471881970303</v>
+        <v>73.59568690790286</v>
       </c>
       <c r="G7" s="5">
         <v>669</v>
       </c>
       <c r="H7" s="5">
-        <v>598</v>
+        <v>361</v>
       </c>
       <c r="I7" s="5">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J7" s="5">
-        <v>61</v>
+        <v>290</v>
       </c>
       <c r="K7" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
+        <v>290</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>-1.238176652071127</v>
+      </c>
+      <c r="O7" s="5">
+        <v>361</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.3037485012452711</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1774091987484568</v>
+      </c>
+      <c r="R7" s="5">
+        <v>361</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="B8" s="4">
-        <v>0.275286593698566</v>
+        <v>0.5801403259429982</v>
       </c>
       <c r="C8" s="4">
-        <v>0.2451325746851163</v>
+        <v>0.4448652452911565</v>
       </c>
       <c r="D8" s="4">
-        <v>0.2118693194917382</v>
+        <v>0.3928387852925546</v>
       </c>
       <c r="E8" s="4">
-        <v>91.95710998153908</v>
+        <v>83.54613964544927</v>
       </c>
       <c r="F8" s="4">
-        <v>88.29568041382888</v>
+        <v>73.78668612725865</v>
       </c>
       <c r="G8" s="5">
         <v>538</v>
       </c>
       <c r="H8" s="5">
-        <v>508</v>
+        <v>313</v>
       </c>
       <c r="I8" s="5">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="J8" s="5">
-        <v>3</v>
+        <v>185</v>
       </c>
       <c r="K8" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L8" s="5">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>-0.4448652452911565</v>
+      </c>
+      <c r="O8" s="5">
+        <v>313</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.3564419319828487</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.2880654680695822</v>
+      </c>
+      <c r="R8" s="5">
+        <v>313</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2118,6 +2422,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2125,7 +2430,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2136,9 +2441,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2172,8 +2483,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2195,255 +2514,381 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5506264055695531</v>
+        <v>1.359211988369509</v>
       </c>
       <c r="C3" s="4">
-        <v>0.530774348465561</v>
+        <v>1.040747269022134</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7110332085307883</v>
+        <v>1.592577659728225</v>
       </c>
       <c r="E3" s="4">
-        <v>90.11319026177819</v>
+        <v>88.96370582617</v>
       </c>
       <c r="F3" s="4">
-        <v>86.73068466632056</v>
+        <v>82.71742210085675</v>
       </c>
       <c r="G3" s="5">
         <v>3490</v>
       </c>
       <c r="H3" s="5">
-        <v>2734</v>
+        <v>1971</v>
       </c>
       <c r="I3" s="5">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="J3" s="5">
-        <v>267</v>
+        <v>1012</v>
       </c>
       <c r="K3" s="5">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L3" s="5">
-        <v>247</v>
+        <v>429</v>
       </c>
       <c r="M3" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>572</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1.340471347416091</v>
+      </c>
+      <c r="O3" s="5">
+        <v>2543</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7126926836092849</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6457208386041666</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2505</v>
+      </c>
+      <c r="S3" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>2.56993064561446</v>
+        <v>0.7773259941232461</v>
       </c>
       <c r="C4" s="4">
-        <v>1.52810929922817</v>
+        <v>0.7795331661404522</v>
       </c>
       <c r="D4" s="4">
-        <v>4.931226246121876</v>
+        <v>0.8007050363370546</v>
       </c>
       <c r="E4" s="4">
-        <v>85.57336473050771</v>
+        <v>89.63194662480382</v>
       </c>
       <c r="F4" s="4">
-        <v>74.82024608501142</v>
+        <v>88.70069695405009</v>
       </c>
       <c r="G4" s="5">
         <v>1300</v>
       </c>
       <c r="H4" s="5">
-        <v>309</v>
+        <v>1282</v>
       </c>
       <c r="I4" s="5">
-        <v>479</v>
+        <v>4</v>
       </c>
       <c r="J4" s="5">
-        <v>512</v>
+        <v>14</v>
       </c>
       <c r="K4" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>185</v>
+        <v>14</v>
       </c>
       <c r="M4" s="5">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.7795331661404522</v>
+      </c>
+      <c r="O4" s="5">
+        <v>1282</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1076514511404432</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1041603434002084</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1282</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4790895030521322</v>
+        <v>0.1367257280337732</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2537311040088182</v>
+        <v>0.1187081056841091</v>
       </c>
       <c r="D5" s="4">
-        <v>3.485966688919773</v>
+        <v>0.1360975668276147</v>
       </c>
       <c r="E5" s="4">
-        <v>85.65913508260437</v>
+        <v>89.12671417773461</v>
       </c>
       <c r="F5" s="4">
-        <v>68.13685593551375</v>
+        <v>86.90205425943722</v>
       </c>
       <c r="G5" s="5">
         <v>1260</v>
       </c>
       <c r="H5" s="5">
-        <v>425</v>
+        <v>1158</v>
       </c>
       <c r="I5" s="5">
-        <v>252</v>
+        <v>63</v>
       </c>
       <c r="J5" s="5">
-        <v>583</v>
+        <v>39</v>
       </c>
       <c r="K5" s="5">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="L5" s="5">
-        <v>540</v>
+        <v>19</v>
       </c>
       <c r="M5" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.04115628920041</v>
+      </c>
+      <c r="O5" s="5">
+        <v>1158</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1358486702103686</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1189852525546344</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1158</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
-        <v>0.1150225418184289</v>
+        <v>0.2758669290680116</v>
       </c>
       <c r="C6" s="4">
-        <v>0.1136553612421478</v>
+        <v>0.2732306190922615</v>
       </c>
       <c r="D6" s="4">
-        <v>0.108963456692414</v>
+        <v>0.2812357022797321</v>
       </c>
       <c r="E6" s="4">
-        <v>89.8420294226065</v>
+        <v>89.86605676753472</v>
       </c>
       <c r="F6" s="4">
-        <v>89.32747049294134</v>
+        <v>88.84360983458363</v>
       </c>
       <c r="G6" s="5">
         <v>1015</v>
       </c>
       <c r="H6" s="5">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="I6" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J6" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>0.2713114394641331</v>
+      </c>
+      <c r="O6" s="5">
+        <v>1008</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.12192128376442</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1169676374100118</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1008</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
-        <v>0.1998262047891307</v>
+        <v>0.1904512549905687</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1647442951226871</v>
+        <v>0.1719305890793098</v>
       </c>
       <c r="D7" s="4">
-        <v>0.166225294840456</v>
+        <v>0.1458937164910269</v>
       </c>
       <c r="E7" s="4">
-        <v>88.88360127309519</v>
+        <v>88.82858973185687</v>
       </c>
       <c r="F7" s="4">
-        <v>84.82576084375955</v>
+        <v>84.55605046765972</v>
       </c>
       <c r="G7" s="5">
         <v>669</v>
       </c>
       <c r="H7" s="5">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="I7" s="5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J7" s="5">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="K7" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" s="5">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.1069990296538559</v>
+      </c>
+      <c r="O7" s="5">
+        <v>608</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1545957607683498</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1406224868223317</v>
+      </c>
+      <c r="R7" s="5">
+        <v>608</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
-        <v>0.1063980208147256</v>
+        <v>0.3148760101653681</v>
       </c>
       <c r="C8" s="4">
-        <v>0.09124914443046996</v>
+        <v>0.3145416642316777</v>
       </c>
       <c r="D8" s="4">
-        <v>0.1018576671943125</v>
+        <v>0.3369432878492517</v>
       </c>
       <c r="E8" s="4">
-        <v>89.94069746857851</v>
+        <v>89.79977492855878</v>
       </c>
       <c r="F8" s="4">
-        <v>89.11560340310895</v>
+        <v>88.23318197317087</v>
       </c>
       <c r="G8" s="5">
         <v>538</v>
       </c>
       <c r="H8" s="5">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="I8" s="5">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J8" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K8" s="5">
         <v>2</v>
       </c>
       <c r="L8" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>0.2952828775998159</v>
+      </c>
+      <c r="O8" s="5">
+        <v>514</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1676316154865241</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.156513082652433</v>
+      </c>
+      <c r="R8" s="5">
+        <v>514</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2454,6 +2899,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2461,7 +2907,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2472,9 +2918,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2508,8 +2960,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2531,157 +2991,229 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>1.27255511560179</v>
+        <v>0.803182596080712</v>
       </c>
       <c r="C3" s="4">
-        <v>0.8619073457167552</v>
+        <v>0.5780735837606271</v>
       </c>
       <c r="D3" s="4">
-        <v>1.487272125249041</v>
+        <v>0.7814287548181286</v>
       </c>
       <c r="E3" s="4">
-        <v>87.26279164961129</v>
+        <v>88.47026489678967</v>
       </c>
       <c r="F3" s="4">
-        <v>83.43889540585752</v>
+        <v>77.59973526150158</v>
       </c>
       <c r="G3" s="5">
         <v>3490</v>
       </c>
       <c r="H3" s="5">
-        <v>2061</v>
+        <v>1665</v>
       </c>
       <c r="I3" s="5">
-        <v>579</v>
+        <v>909</v>
       </c>
       <c r="J3" s="5">
-        <v>850</v>
+        <v>916</v>
       </c>
       <c r="K3" s="5">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="L3" s="5">
-        <v>290</v>
+        <v>863</v>
       </c>
       <c r="M3" s="5">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>23</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.05763792853148651</v>
+      </c>
+      <c r="O3" s="5">
+        <v>1688</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7882413285243748</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5815470782861492</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1669</v>
+      </c>
+      <c r="S3" s="5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>1.773486660010601</v>
+        <v>2.479684247662037</v>
       </c>
       <c r="C4" s="4">
-        <v>1.778952192530623</v>
+        <v>1.733694535083582</v>
       </c>
       <c r="D4" s="4">
-        <v>2.263781244896855</v>
+        <v>7.970300430476597</v>
       </c>
       <c r="E4" s="4">
-        <v>84.72587650444792</v>
+        <v>83.64358974358983</v>
       </c>
       <c r="F4" s="4">
-        <v>76.45103252452219</v>
+        <v>61.00218551023918</v>
       </c>
       <c r="G4" s="5">
         <v>1300</v>
       </c>
       <c r="H4" s="5">
-        <v>527</v>
+        <v>205</v>
       </c>
       <c r="I4" s="5">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J4" s="5">
-        <v>661</v>
+        <v>985</v>
       </c>
       <c r="K4" s="5">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="L4" s="5">
-        <v>370</v>
+        <v>845</v>
       </c>
       <c r="M4" s="5">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>110</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1.937136505082173</v>
+      </c>
+      <c r="O4" s="5">
+        <v>315</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.7508733222117771</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2666675621592036</v>
+      </c>
+      <c r="R4" s="5">
+        <v>315</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4772163542646089</v>
+        <v>0.2926986232194212</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5058072010045613</v>
+        <v>0.1950118682450668</v>
       </c>
       <c r="D5" s="4">
-        <v>0.7338276427507948</v>
+        <v>0.622406754775047</v>
       </c>
       <c r="E5" s="4">
-        <v>86.25102580714822</v>
+        <v>89.88483965014582</v>
       </c>
       <c r="F5" s="4">
-        <v>81.54237242995622</v>
+        <v>78.13611910088407</v>
       </c>
       <c r="G5" s="5">
         <v>1260</v>
       </c>
       <c r="H5" s="5">
-        <v>1096</v>
+        <v>880</v>
       </c>
       <c r="I5" s="5">
-        <v>122</v>
+        <v>344</v>
       </c>
       <c r="J5" s="5">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="K5" s="5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L5" s="5">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.1018303467243184</v>
+      </c>
+      <c r="O5" s="5">
+        <v>880</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2833188556365575</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2016130586078355</v>
+      </c>
+      <c r="R5" s="5">
+        <v>880</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
-        <v>0.1529998893652104</v>
+        <v>0.182127381600939</v>
       </c>
       <c r="C6" s="4">
-        <v>0.1532833743340228</v>
+        <v>0.1776947214626322</v>
       </c>
       <c r="D6" s="4">
-        <v>0.1727106262954146</v>
+        <v>0.207890135351507</v>
       </c>
       <c r="E6" s="4">
-        <v>87.48145169397809</v>
+        <v>90.65822190945345</v>
       </c>
       <c r="F6" s="4">
-        <v>88.80040995801171</v>
+        <v>84.37246669091054</v>
       </c>
       <c r="G6" s="5">
         <v>1015</v>
       </c>
       <c r="H6" s="5">
-        <v>1011</v>
+        <v>811</v>
       </c>
       <c r="I6" s="5">
-        <v>3</v>
+        <v>203</v>
       </c>
       <c r="J6" s="5">
         <v>1</v>
@@ -2695,91 +3227,145 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.1588468032715709</v>
+      </c>
+      <c r="O6" s="5">
+        <v>811</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1060678523990335</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1037889844910423</v>
+      </c>
+      <c r="R6" s="5">
+        <v>811</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
-        <v>0.241346198578382</v>
+        <v>0.2016252396962697</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1965746234173312</v>
+        <v>0.1921791241875918</v>
       </c>
       <c r="D7" s="4">
-        <v>0.3110146923881992</v>
+        <v>0.2748809197757763</v>
       </c>
       <c r="E7" s="4">
-        <v>86.42287707310129</v>
+        <v>90.96341376610434</v>
       </c>
       <c r="F7" s="4">
-        <v>83.11005440689246</v>
+        <v>85.09471881970303</v>
       </c>
       <c r="G7" s="5">
         <v>669</v>
       </c>
       <c r="H7" s="5">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="I7" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J7" s="5">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="K7" s="5">
         <v>3</v>
       </c>
       <c r="L7" s="5">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>0.03038422267104736</v>
+      </c>
+      <c r="O7" s="5">
+        <v>598</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2049328135928202</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.194754796769448</v>
+      </c>
+      <c r="R7" s="5">
+        <v>598</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
-        <v>0.2299034888952143</v>
+        <v>0.275286593698566</v>
       </c>
       <c r="C8" s="4">
-        <v>0.2249074596914889</v>
+        <v>0.2451325746851163</v>
       </c>
       <c r="D8" s="4">
-        <v>0.2572649304204769</v>
+        <v>0.2118693194917382</v>
       </c>
       <c r="E8" s="4">
-        <v>87.62353640340896</v>
+        <v>91.95710998153908</v>
       </c>
       <c r="F8" s="4">
-        <v>88.78986718561436</v>
+        <v>88.29568041382888</v>
       </c>
       <c r="G8" s="5">
         <v>538</v>
       </c>
       <c r="H8" s="5">
-        <v>529</v>
+        <v>508</v>
       </c>
       <c r="I8" s="5">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="J8" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>-0.1791329848749302</v>
+      </c>
+      <c r="O8" s="5">
+        <v>508</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.2134601708896071</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1894743557397139</v>
+      </c>
+      <c r="R8" s="5">
+        <v>508</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2790,6 +3376,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2797,7 +3384,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2808,9 +3395,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2844,8 +3437,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2867,245 +3468,353 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>2.764803058821582</v>
+        <v>0.5506264055695531</v>
       </c>
       <c r="C3" s="4">
-        <v>1.403792582401377</v>
+        <v>0.530774348465561</v>
       </c>
       <c r="D3" s="4">
-        <v>2.424038191208167</v>
+        <v>0.7110332085307883</v>
       </c>
       <c r="E3" s="4">
-        <v>87.77100754341845</v>
+        <v>90.11319026177819</v>
       </c>
       <c r="F3" s="4">
-        <v>80.0075543419036</v>
+        <v>86.73068466632056</v>
       </c>
       <c r="G3" s="5">
         <v>3490</v>
       </c>
       <c r="H3" s="5">
-        <v>568</v>
+        <v>2734</v>
       </c>
       <c r="I3" s="5">
-        <v>638</v>
+        <v>489</v>
       </c>
       <c r="J3" s="5">
-        <v>2284</v>
+        <v>267</v>
       </c>
       <c r="K3" s="5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L3" s="5">
-        <v>533</v>
+        <v>247</v>
       </c>
       <c r="M3" s="5">
-        <v>1733</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>4</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.3534800899030155</v>
+      </c>
+      <c r="O3" s="5">
+        <v>2738</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4897177643666333</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4614282593230028</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2738</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>3.496828837870044</v>
+        <v>2.56993064561446</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
+        <v>1.52810929922817</v>
       </c>
       <c r="D4" s="4">
-        <v>8.937304556511847</v>
+        <v>4.931226246121876</v>
       </c>
       <c r="E4" s="4">
-        <v>72.20884353741495</v>
+        <v>85.57336473050771</v>
       </c>
       <c r="F4" s="4">
-        <v>47.79626570297693</v>
+        <v>74.82024608501142</v>
       </c>
       <c r="G4" s="5">
         <v>1300</v>
       </c>
       <c r="H4" s="5">
-        <v>0</v>
+        <v>309</v>
       </c>
       <c r="I4" s="5">
-        <v>107</v>
+        <v>479</v>
       </c>
       <c r="J4" s="5">
-        <v>1193</v>
+        <v>512</v>
       </c>
       <c r="K4" s="5">
-        <v>155</v>
+        <v>8</v>
       </c>
       <c r="L4" s="5">
-        <v>1037</v>
+        <v>185</v>
       </c>
       <c r="M4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>319</v>
+      </c>
+      <c r="N4" s="4">
+        <v>2.164181263319821</v>
+      </c>
+      <c r="O4" s="5">
+        <v>628</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8964630067182358</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6026177890816858</v>
+      </c>
+      <c r="R4" s="5">
+        <v>617</v>
+      </c>
+      <c r="S4" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>1.351248198474225</v>
+        <v>0.4790895030521322</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4806994894445838</v>
+        <v>0.2537311040088182</v>
       </c>
       <c r="D5" s="4">
-        <v>3.823875724016405</v>
+        <v>3.485966688919773</v>
       </c>
       <c r="E5" s="4">
-        <v>83.36227189288427</v>
+        <v>85.65913508260437</v>
       </c>
       <c r="F5" s="4">
-        <v>54.83726607719883</v>
+        <v>68.13685593551375</v>
       </c>
       <c r="G5" s="5">
         <v>1260</v>
       </c>
       <c r="H5" s="5">
-        <v>101</v>
+        <v>425</v>
       </c>
       <c r="I5" s="5">
-        <v>192</v>
+        <v>252</v>
       </c>
       <c r="J5" s="5">
-        <v>967</v>
+        <v>583</v>
       </c>
       <c r="K5" s="5">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L5" s="5">
-        <v>934</v>
+        <v>540</v>
       </c>
       <c r="M5" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+        <v>14</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.1041533110146466</v>
+      </c>
+      <c r="O5" s="5">
+        <v>439</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4867380587164908</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1756163186679031</v>
+      </c>
+      <c r="R5" s="5">
+        <v>425</v>
+      </c>
+      <c r="S5" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
-        <v>0.4773089667212967</v>
+        <v>0.1150225418184289</v>
       </c>
       <c r="C6" s="4">
-        <v>0.4757829290814142</v>
+        <v>0.1136553612421478</v>
       </c>
       <c r="D6" s="4">
-        <v>0.5369629095951763</v>
+        <v>0.108963456692414</v>
       </c>
       <c r="E6" s="4">
-        <v>92.96990717469254</v>
+        <v>89.8420294226065</v>
       </c>
       <c r="F6" s="4">
-        <v>90.46216153668176</v>
+        <v>89.32747049294134</v>
       </c>
       <c r="G6" s="5">
         <v>1015</v>
       </c>
       <c r="H6" s="5">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="I6" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.05283755987624283</v>
+      </c>
+      <c r="O6" s="5">
+        <v>1010</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1125907659502703</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1114731189581876</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1010</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
-        <v>0.2963155911239383</v>
+        <v>0.1998262047891307</v>
       </c>
       <c r="C7" s="4">
-        <v>0.2628612307436877</v>
+        <v>0.1647442951226871</v>
       </c>
       <c r="D7" s="4">
-        <v>0.1971065602968905</v>
+        <v>0.166225294840456</v>
       </c>
       <c r="E7" s="4">
-        <v>91.16561422775386</v>
+        <v>88.88360127309519</v>
       </c>
       <c r="F7" s="4">
-        <v>86.56841992623201</v>
+        <v>84.82576084375955</v>
       </c>
       <c r="G7" s="5">
         <v>669</v>
       </c>
       <c r="H7" s="5">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="I7" s="5">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="J7" s="5">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="K7" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" s="5">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.08428179642163802</v>
+      </c>
+      <c r="O7" s="5">
+        <v>591</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1902665180964928</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1519777999693841</v>
+      </c>
+      <c r="R7" s="5">
+        <v>591</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
-        <v>0.3035960562892668</v>
+        <v>0.1063980208147256</v>
       </c>
       <c r="C8" s="4">
-        <v>0.2267828529867313</v>
+        <v>0.09124914443046996</v>
       </c>
       <c r="D8" s="4">
-        <v>0.2447872951367857</v>
+        <v>0.1018576671943125</v>
       </c>
       <c r="E8" s="4">
-        <v>92.52061047467315</v>
+        <v>89.94069746857851</v>
       </c>
       <c r="F8" s="4">
-        <v>87.13436541004394</v>
+        <v>89.11560340310895</v>
       </c>
       <c r="G8" s="5">
         <v>538</v>
       </c>
       <c r="H8" s="5">
-        <v>476</v>
+        <v>522</v>
       </c>
       <c r="I8" s="5">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="J8" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L8" s="5">
         <v>0</v>
@@ -3113,9 +3822,27 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>-0.02337691061890905</v>
+      </c>
+      <c r="O8" s="5">
+        <v>522</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1109844759994347</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.09651358086112208</v>
+      </c>
+      <c r="R8" s="5">
+        <v>522</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3126,6 +3853,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3133,7 +3861,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3144,9 +3872,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -3180,8 +3914,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3203,239 +3945,347 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>2.891002932916023</v>
+        <v>1.27255511560179</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4947285959199219</v>
+        <v>0.8619073457167552</v>
       </c>
       <c r="D3" s="4">
-        <v>1.552019930606428</v>
+        <v>1.487272125249041</v>
       </c>
       <c r="E3" s="4">
-        <v>95.34089624388449</v>
+        <v>87.26279164961129</v>
       </c>
       <c r="F3" s="4">
-        <v>92.40850175958103</v>
+        <v>83.43889540585752</v>
       </c>
       <c r="G3" s="5">
         <v>3490</v>
       </c>
       <c r="H3" s="5">
-        <v>163</v>
+        <v>2061</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>579</v>
       </c>
       <c r="J3" s="5">
-        <v>3327</v>
+        <v>850</v>
       </c>
       <c r="K3" s="5">
-        <v>3325</v>
+        <v>22</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>290</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>538</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1.118697946459242</v>
+      </c>
+      <c r="O3" s="5">
+        <v>2599</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8153886011401899</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7570084175376214</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2540</v>
+      </c>
+      <c r="S3" s="5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7482551291543595</v>
+        <v>1.773486660010601</v>
       </c>
       <c r="C4" s="4">
-        <v>0.7503207131464761</v>
+        <v>1.778952192530623</v>
       </c>
       <c r="D4" s="4">
-        <v>0.7708946075392725</v>
+        <v>2.263781244896855</v>
       </c>
       <c r="E4" s="4">
-        <v>95.95572998430141</v>
+        <v>84.72587650444792</v>
       </c>
       <c r="F4" s="4">
-        <v>93.5761744966439</v>
+        <v>76.45103252452219</v>
       </c>
       <c r="G4" s="5">
         <v>1300</v>
       </c>
       <c r="H4" s="5">
-        <v>1237</v>
+        <v>527</v>
       </c>
       <c r="I4" s="5">
-        <v>3</v>
+        <v>112</v>
       </c>
       <c r="J4" s="5">
-        <v>60</v>
+        <v>661</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L4" s="5">
-        <v>60</v>
+        <v>370</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>276</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1.901171529572975</v>
+      </c>
+      <c r="O4" s="5">
+        <v>803</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2411645845076773</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1783692025888824</v>
+      </c>
+      <c r="R4" s="5">
+        <v>803</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1317187189717575</v>
+        <v>0.4772163542646089</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1140849909379121</v>
+        <v>0.5058072010045613</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1221700070579779</v>
+        <v>0.7338276427507948</v>
       </c>
       <c r="E5" s="4">
-        <v>96.00747759421229</v>
+        <v>86.25102580714822</v>
       </c>
       <c r="F5" s="4">
-        <v>93.45847093497885</v>
+        <v>81.54237242995622</v>
       </c>
       <c r="G5" s="5">
         <v>1260</v>
       </c>
       <c r="H5" s="5">
-        <v>1185</v>
+        <v>1096</v>
       </c>
       <c r="I5" s="5">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="J5" s="5">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="K5" s="5">
         <v>2</v>
       </c>
       <c r="L5" s="5">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>0.4539332579838726</v>
+      </c>
+      <c r="O5" s="5">
+        <v>1096</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2808264305107054</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2786843037414828</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1096</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
-        <v>0.3704960263173042</v>
+        <v>0.1529998893652104</v>
       </c>
       <c r="C6" s="4">
-        <v>0.3704960263173042</v>
+        <v>0.1532833743340228</v>
       </c>
       <c r="D6" s="4">
-        <v>0.3864582155113258</v>
+        <v>0.1727106262954146</v>
       </c>
       <c r="E6" s="4">
-        <v>96.32844073590029</v>
+        <v>87.48145169397809</v>
       </c>
       <c r="F6" s="4">
-        <v>94.96925314907266</v>
+        <v>88.80040995801171</v>
       </c>
       <c r="G6" s="5">
         <v>1015</v>
       </c>
       <c r="H6" s="5">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="I6" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>0.1002998381523428</v>
+      </c>
+      <c r="O6" s="5">
+        <v>1011</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1008274104985462</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1007060590758933</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1011</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
-        <v>0.2075784363032758</v>
+        <v>0.241346198578382</v>
       </c>
       <c r="C7" s="4">
-        <v>0.2046725784222334</v>
+        <v>0.1965746234173312</v>
       </c>
       <c r="D7" s="4">
-        <v>0.2534935097227261</v>
+        <v>0.3110146923881992</v>
       </c>
       <c r="E7" s="4">
-        <v>95.22192733595679</v>
+        <v>86.42287707310129</v>
       </c>
       <c r="F7" s="4">
-        <v>91.3363462779601</v>
+        <v>83.11005440689246</v>
       </c>
       <c r="G7" s="5">
         <v>669</v>
       </c>
       <c r="H7" s="5">
-        <v>636</v>
+        <v>600</v>
       </c>
       <c r="I7" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J7" s="5">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="K7" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" s="5">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>0.1308045465188028</v>
+      </c>
+      <c r="O7" s="5">
+        <v>600</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2267887489929764</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1812167371537654</v>
+      </c>
+      <c r="R7" s="5">
+        <v>600</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
-        <v>0.1723244560170566</v>
+        <v>0.2299034888952143</v>
       </c>
       <c r="C8" s="4">
-        <v>0.1723244560170566</v>
+        <v>0.2249074596914889</v>
       </c>
       <c r="D8" s="4">
-        <v>0.1788174222850907</v>
+        <v>0.2572649304204769</v>
       </c>
       <c r="E8" s="4">
-        <v>96.3690792302051</v>
+        <v>87.62353640340896</v>
       </c>
       <c r="F8" s="4">
-        <v>94.95542360054222</v>
+        <v>88.78986718561436</v>
       </c>
       <c r="G8" s="5">
         <v>538</v>
       </c>
       <c r="H8" s="5">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="I8" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J8" s="5">
         <v>0</v>
@@ -3449,9 +4299,27 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>0.2091117579193037</v>
+      </c>
+      <c r="O8" s="5">
+        <v>529</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1367591073223806</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1266207241386377</v>
+      </c>
+      <c r="R8" s="5">
+        <v>529</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3462,6 +4330,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3469,7 +4338,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3480,9 +4349,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -3516,8 +4391,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3539,157 +4422,223 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1974515271931606</v>
+        <v>2.764803058821582</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1583712902778543</v>
+        <v>1.403792582401377</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3181694708718721</v>
+        <v>2.424038191208167</v>
       </c>
       <c r="E3" s="4">
-        <v>91.56970352610955</v>
+        <v>87.77100754341845</v>
       </c>
       <c r="F3" s="4">
-        <v>91.3202053806662</v>
+        <v>80.0075543419036</v>
       </c>
       <c r="G3" s="5">
         <v>3490</v>
       </c>
       <c r="H3" s="5">
-        <v>3238</v>
+        <v>568</v>
       </c>
       <c r="I3" s="5">
-        <v>145</v>
+        <v>638</v>
       </c>
       <c r="J3" s="5">
-        <v>107</v>
+        <v>2284</v>
       </c>
       <c r="K3" s="5">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="L3" s="5">
-        <v>103</v>
+        <v>533</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>1733</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-2.481246926873636</v>
+      </c>
+      <c r="O3" s="5">
+        <v>2301</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7670972158662838</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6161763011326012</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2285</v>
+      </c>
+      <c r="S3" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>0.9476822151306323</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.9442397940292493</v>
-      </c>
+        <v>3.496828837870044</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.9578385326999368</v>
+        <v>8.937304556511847</v>
       </c>
       <c r="E4" s="4">
-        <v>88.75750915750926</v>
+        <v>72.20884353741495</v>
       </c>
       <c r="F4" s="4">
-        <v>89.83342798141202</v>
+        <v>47.79626570297693</v>
       </c>
       <c r="G4" s="5">
         <v>1300</v>
       </c>
       <c r="H4" s="5">
-        <v>1232</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="J4" s="5">
-        <v>68</v>
+        <v>1193</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="L4" s="5">
-        <v>68</v>
+        <v>1037</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>3.496828837870044</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>0.253016501161246</v>
+        <v>1.351248198474225</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2352381099736341</v>
+        <v>0.4806994894445838</v>
       </c>
       <c r="D5" s="4">
-        <v>0.237106504846164</v>
+        <v>3.823875724016405</v>
       </c>
       <c r="E5" s="4">
-        <v>88.84205269409348</v>
+        <v>83.36227189288427</v>
       </c>
       <c r="F5" s="4">
-        <v>90.24653776499441</v>
+        <v>54.83726607719883</v>
       </c>
       <c r="G5" s="5">
         <v>1260</v>
       </c>
       <c r="H5" s="5">
-        <v>1206</v>
+        <v>101</v>
       </c>
       <c r="I5" s="5">
-        <v>42</v>
+        <v>192</v>
       </c>
       <c r="J5" s="5">
+        <v>967</v>
+      </c>
+      <c r="K5" s="5">
+        <v>21</v>
+      </c>
+      <c r="L5" s="5">
+        <v>934</v>
+      </c>
+      <c r="M5" s="5">
         <v>12</v>
       </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
+      <c r="N5" s="4">
+        <v>0.7078335553130313</v>
+      </c>
+      <c r="O5" s="5">
+        <v>113</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.8834608908113242</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.339943618951194</v>
+      </c>
+      <c r="R5" s="5">
+        <v>101</v>
+      </c>
+      <c r="S5" s="5">
         <v>12</v>
       </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
-        <v>0.2860368277255486</v>
+        <v>0.4773089667212967</v>
       </c>
       <c r="C6" s="4">
-        <v>0.2855143406149649</v>
+        <v>0.4757829290814142</v>
       </c>
       <c r="D6" s="4">
-        <v>0.2788263468343599</v>
+        <v>0.5369629095951763</v>
       </c>
       <c r="E6" s="4">
-        <v>88.46127810730205</v>
+        <v>92.96990717469254</v>
       </c>
       <c r="F6" s="4">
-        <v>90.2234932389994</v>
+        <v>90.46216153668176</v>
       </c>
       <c r="G6" s="5">
         <v>1015</v>
       </c>
       <c r="H6" s="5">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="I6" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J6" s="5">
         <v>0</v>
@@ -3703,81 +4652,117 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.4757829290814142</v>
+      </c>
+      <c r="O6" s="5">
+        <v>1005</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1022224737137491</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1016983906616663</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1005</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
-        <v>0.2177916831408122</v>
+        <v>0.2963155911239383</v>
       </c>
       <c r="C7" s="4">
-        <v>0.2224547373208095</v>
+        <v>0.2628612307436877</v>
       </c>
       <c r="D7" s="4">
-        <v>0.2144772958617414</v>
+        <v>0.1971065602968905</v>
       </c>
       <c r="E7" s="4">
-        <v>88.82375969819915</v>
+        <v>91.16561422775386</v>
       </c>
       <c r="F7" s="4">
-        <v>88.35127389706496</v>
+        <v>86.56841992623201</v>
       </c>
       <c r="G7" s="5">
         <v>669</v>
       </c>
       <c r="H7" s="5">
-        <v>644</v>
+        <v>605</v>
       </c>
       <c r="I7" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J7" s="5">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.07382133599858602</v>
+      </c>
+      <c r="O7" s="5">
+        <v>605</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2870047423268561</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.2562259947680011</v>
+      </c>
+      <c r="R7" s="5">
+        <v>605</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
-        <v>0.06970973428608244</v>
+        <v>0.3035960562892668</v>
       </c>
       <c r="C8" s="4">
-        <v>0.06590856913574759</v>
+        <v>0.2267828529867313</v>
       </c>
       <c r="D8" s="4">
-        <v>0.06957059557450772</v>
+        <v>0.2447872951367857</v>
       </c>
       <c r="E8" s="4">
-        <v>89.23551576764534</v>
+        <v>92.52061047467315</v>
       </c>
       <c r="F8" s="4">
-        <v>90.83665993030588</v>
+        <v>87.13436541004394</v>
       </c>
       <c r="G8" s="5">
         <v>538</v>
       </c>
       <c r="H8" s="5">
-        <v>534</v>
+        <v>476</v>
       </c>
       <c r="I8" s="5">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="J8" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" s="5">
         <v>0</v>
@@ -3785,9 +4770,27 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>-0.2195908009011196</v>
+      </c>
+      <c r="O8" s="5">
+        <v>476</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1698251254429213</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1031866750699875</v>
+      </c>
+      <c r="R8" s="5">
+        <v>476</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3798,6 +4801,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3805,7 +4809,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3816,9 +4820,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -3852,8 +4862,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3875,157 +4893,229 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4417525106672162</v>
+        <v>2.891002932916023</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3753706015585704</v>
+        <v>0.4947285959199219</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4774553592662575</v>
+        <v>1.552019930606428</v>
       </c>
       <c r="E3" s="4">
-        <v>90.83188117653955</v>
+        <v>95.34089624388449</v>
       </c>
       <c r="F3" s="4">
-        <v>86.31019275270336</v>
+        <v>92.40850175958103</v>
       </c>
       <c r="G3" s="5">
         <v>3490</v>
       </c>
       <c r="H3" s="5">
-        <v>2728</v>
+        <v>163</v>
       </c>
       <c r="I3" s="5">
-        <v>507</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>255</v>
+        <v>3327</v>
       </c>
       <c r="K3" s="5">
-        <v>14</v>
+        <v>3325</v>
       </c>
       <c r="L3" s="5">
-        <v>234</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.4947285959199219</v>
+      </c>
+      <c r="O3" s="5">
+        <v>163</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2.409049882596162</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1147080497348605</v>
+      </c>
+      <c r="R3" s="5">
+        <v>163</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6747811423552754</v>
+        <v>0.7482551291543595</v>
       </c>
       <c r="C4" s="4">
-        <v>0.7109741981742077</v>
+        <v>0.7503207131464761</v>
       </c>
       <c r="D4" s="4">
-        <v>0.802682048866309</v>
+        <v>0.7708946075392725</v>
       </c>
       <c r="E4" s="4">
-        <v>93.20431711145999</v>
+        <v>95.95572998430141</v>
       </c>
       <c r="F4" s="4">
-        <v>90.0463603510585</v>
+        <v>93.5761744966439</v>
       </c>
       <c r="G4" s="5">
         <v>1300</v>
       </c>
       <c r="H4" s="5">
-        <v>1154</v>
+        <v>1237</v>
       </c>
       <c r="I4" s="5">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
-        <v>119</v>
+        <v>60</v>
       </c>
       <c r="K4" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.7503207131464761</v>
+      </c>
+      <c r="O4" s="5">
+        <v>1237</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.06942382153160326</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06554026005108625</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1237</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1505771420582873</v>
+        <v>0.1317187189717575</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1280034346839128</v>
+        <v>0.1140849909379121</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1728915584122243</v>
+        <v>0.1221700070579779</v>
       </c>
       <c r="E5" s="4">
-        <v>93.36224489795917</v>
+        <v>96.00747759421229</v>
       </c>
       <c r="F5" s="4">
-        <v>89.79982955150734</v>
+        <v>93.45847093497885</v>
       </c>
       <c r="G5" s="5">
         <v>1260</v>
       </c>
       <c r="H5" s="5">
-        <v>1065</v>
+        <v>1185</v>
       </c>
       <c r="I5" s="5">
-        <v>154</v>
+        <v>61</v>
       </c>
       <c r="J5" s="5">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>0.08326877389428296</v>
+      </c>
+      <c r="O5" s="5">
+        <v>1185</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1117159937894823</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.08774269289760581</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1185</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
-        <v>0.183661732487953</v>
+        <v>0.3704960263173042</v>
       </c>
       <c r="C6" s="4">
-        <v>0.1840205833169233</v>
+        <v>0.3704960263173042</v>
       </c>
       <c r="D6" s="4">
-        <v>0.2435730046703571</v>
+        <v>0.3864582155113258</v>
       </c>
       <c r="E6" s="4">
-        <v>93.63804832277741</v>
+        <v>96.32844073590029</v>
       </c>
       <c r="F6" s="4">
-        <v>93.35585898325949</v>
+        <v>94.96925314907266</v>
       </c>
       <c r="G6" s="5">
         <v>1015</v>
       </c>
       <c r="H6" s="5">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="I6" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6" s="5">
         <v>0</v>
@@ -4039,91 +5129,145 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>0.3669918589589638</v>
+      </c>
+      <c r="O6" s="5">
+        <v>1015</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.04662348765435286</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.04455373094265427</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1014</v>
+      </c>
+      <c r="S6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
-        <v>0.3521454459821016</v>
+        <v>0.2075784363032758</v>
       </c>
       <c r="C7" s="4">
-        <v>0.350870891986996</v>
+        <v>0.2046725784222334</v>
       </c>
       <c r="D7" s="4">
-        <v>0.467592281412627</v>
+        <v>0.2534935097227261</v>
       </c>
       <c r="E7" s="4">
-        <v>92.3548193567412</v>
+        <v>95.22192733595679</v>
       </c>
       <c r="F7" s="4">
-        <v>88.47675752316685</v>
+        <v>91.3363462779601</v>
       </c>
       <c r="G7" s="5">
         <v>669</v>
       </c>
       <c r="H7" s="5">
-        <v>575</v>
+        <v>636</v>
       </c>
       <c r="I7" s="5">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J7" s="5">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="K7" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" s="5">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>0.1852920584706903</v>
+      </c>
+      <c r="O7" s="5">
+        <v>636</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1386281125991836</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1337772494741122</v>
+      </c>
+      <c r="R7" s="5">
+        <v>636</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
-        <v>0.2047560100984644</v>
+        <v>0.1723244560170566</v>
       </c>
       <c r="C8" s="4">
-        <v>0.1851903673788913</v>
+        <v>0.1723244560170566</v>
       </c>
       <c r="D8" s="4">
-        <v>0.2420165575316716</v>
+        <v>0.1788174222850907</v>
       </c>
       <c r="E8" s="4">
-        <v>93.82634094530006</v>
+        <v>96.3690792302051</v>
       </c>
       <c r="F8" s="4">
-        <v>91.91591194497639</v>
+        <v>94.95542360054222</v>
       </c>
       <c r="G8" s="5">
         <v>538</v>
       </c>
       <c r="H8" s="5">
-        <v>503</v>
+        <v>538</v>
       </c>
       <c r="I8" s="5">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J8" s="5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L8" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>0.1643482298759468</v>
+      </c>
+      <c r="O8" s="5">
+        <v>538</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.07004150844253584</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.07004150844253584</v>
+      </c>
+      <c r="R8" s="5">
+        <v>538</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4134,6 +5278,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4141,7 +5286,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4152,9 +5297,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -4188,8 +5339,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4211,148 +5370,220 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>1.036238909405371</v>
+        <v>0.1974515271931606</v>
       </c>
       <c r="C3" s="4">
-        <v>0.9731148121978462</v>
+        <v>0.1583712902778543</v>
       </c>
       <c r="D3" s="4">
-        <v>1.120655116299837</v>
+        <v>0.3181694708718721</v>
       </c>
       <c r="E3" s="4">
-        <v>90.35276689472352</v>
+        <v>91.56970352610955</v>
       </c>
       <c r="F3" s="4">
-        <v>87.29020275251118</v>
+        <v>91.3202053806662</v>
       </c>
       <c r="G3" s="5">
         <v>3490</v>
       </c>
       <c r="H3" s="5">
-        <v>2527</v>
+        <v>3238</v>
       </c>
       <c r="I3" s="5">
-        <v>397</v>
+        <v>145</v>
       </c>
       <c r="J3" s="5">
-        <v>566</v>
+        <v>107</v>
       </c>
       <c r="K3" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L3" s="5">
-        <v>395</v>
+        <v>103</v>
       </c>
       <c r="M3" s="5">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.02406139210791815</v>
+      </c>
+      <c r="O3" s="5">
+        <v>3238</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1953917440146855</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1575311146566742</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3238</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4834003091289333</v>
+        <v>0.9476822151306323</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4858857864286872</v>
+        <v>0.9442397940292493</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5373773054569767</v>
+        <v>0.9578385326999368</v>
       </c>
       <c r="E4" s="4">
-        <v>90.79246467817897</v>
+        <v>88.75750915750926</v>
       </c>
       <c r="F4" s="4">
-        <v>89.6296764756493</v>
+        <v>89.83342798141202</v>
       </c>
       <c r="G4" s="5">
         <v>1300</v>
       </c>
       <c r="H4" s="5">
-        <v>1259</v>
+        <v>1232</v>
       </c>
       <c r="I4" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.9442397940292493</v>
+      </c>
+      <c r="O4" s="5">
+        <v>1232</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.05519194154958425</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.05019900923391741</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1232</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1518970015853073</v>
+        <v>0.253016501161246</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1309823756418455</v>
+        <v>0.2352381099736341</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1281928934472783</v>
+        <v>0.237106504846164</v>
       </c>
       <c r="E5" s="4">
-        <v>90.94374257639566</v>
+        <v>88.84205269409348</v>
       </c>
       <c r="F5" s="4">
-        <v>88.98646177337439</v>
+        <v>90.24653776499441</v>
       </c>
       <c r="G5" s="5">
         <v>1260</v>
       </c>
       <c r="H5" s="5">
-        <v>1185</v>
+        <v>1206</v>
       </c>
       <c r="I5" s="5">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="J5" s="5">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.2349149395955698</v>
+      </c>
+      <c r="O5" s="5">
+        <v>1206</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.09839540306392432</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.08421225851056233</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1206</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
-        <v>0.1881001581961826</v>
+        <v>0.2860368277255486</v>
       </c>
       <c r="C6" s="4">
-        <v>0.1881623030204206</v>
+        <v>0.2855143406149649</v>
       </c>
       <c r="D6" s="4">
-        <v>0.1955659717746267</v>
+        <v>0.2788263468343599</v>
       </c>
       <c r="E6" s="4">
-        <v>90.95693844040079</v>
+        <v>88.46127810730205</v>
       </c>
       <c r="F6" s="4">
-        <v>90.49177328881113</v>
+        <v>90.2234932389994</v>
       </c>
       <c r="G6" s="5">
         <v>1015</v>
@@ -4361,89 +5592,125 @@
         <v>1011</v>
       </c>
       <c r="I6" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J6" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.2855143406149649</v>
+      </c>
+      <c r="O6" s="5">
+        <v>1011</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.06718182122968165</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.06692307035695796</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1011</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
-        <v>0.1564620508023996</v>
+        <v>0.2177916831408122</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1303017611922076</v>
+        <v>0.2224547373208095</v>
       </c>
       <c r="D7" s="4">
-        <v>0.1583719914497226</v>
+        <v>0.2144772958617414</v>
       </c>
       <c r="E7" s="4">
-        <v>90.4063837792217</v>
+        <v>88.82375969819915</v>
       </c>
       <c r="F7" s="4">
-        <v>87.95586253482045</v>
+        <v>88.35127389706496</v>
       </c>
       <c r="G7" s="5">
         <v>669</v>
       </c>
       <c r="H7" s="5">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="I7" s="5">
         <v>0</v>
       </c>
       <c r="J7" s="5">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="K7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.2099001125602958</v>
+      </c>
+      <c r="O7" s="5">
+        <v>644</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1234517403621946</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1203799960571975</v>
+      </c>
+      <c r="R7" s="5">
+        <v>644</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
-        <v>0.1429144716529124</v>
+        <v>0.06970973428608244</v>
       </c>
       <c r="C8" s="4">
-        <v>0.1376156927300987</v>
+        <v>0.06590856913574759</v>
       </c>
       <c r="D8" s="4">
-        <v>0.1506999249734916</v>
+        <v>0.06957059557450772</v>
       </c>
       <c r="E8" s="4">
-        <v>91.54338315251751</v>
+        <v>89.23551576764534</v>
       </c>
       <c r="F8" s="4">
-        <v>90.99454853920673</v>
+        <v>90.83665993030588</v>
       </c>
       <c r="G8" s="5">
         <v>538</v>
       </c>
       <c r="H8" s="5">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="I8" s="5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J8" s="5">
         <v>0</v>
@@ -4457,9 +5724,27 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>-0.05245341512409068</v>
+      </c>
+      <c r="O8" s="5">
+        <v>534</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.05841384024738318</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.05492097113514113</v>
+      </c>
+      <c r="R8" s="5">
+        <v>534</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4470,12 +5755,1874 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.4417525106672162</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3753706015585704</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.4774553592662575</v>
+      </c>
+      <c r="E3" s="4">
+        <v>90.83188117653955</v>
+      </c>
+      <c r="F3" s="4">
+        <v>86.31019275270336</v>
+      </c>
+      <c r="G3" s="5">
+        <v>3490</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2728</v>
+      </c>
+      <c r="I3" s="5">
+        <v>507</v>
+      </c>
+      <c r="J3" s="5">
+        <v>255</v>
+      </c>
+      <c r="K3" s="5">
+        <v>14</v>
+      </c>
+      <c r="L3" s="5">
+        <v>234</v>
+      </c>
+      <c r="M3" s="5">
+        <v>7</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.08366530479387449</v>
+      </c>
+      <c r="O3" s="5">
+        <v>2735</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4455541591892289</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3733592419057173</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2729</v>
+      </c>
+      <c r="S3" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.6747811423552754</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.7109741981742077</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.802682048866309</v>
+      </c>
+      <c r="E4" s="4">
+        <v>93.20431711145999</v>
+      </c>
+      <c r="F4" s="4">
+        <v>90.0463603510585</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1300</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1154</v>
+      </c>
+      <c r="I4" s="5">
+        <v>27</v>
+      </c>
+      <c r="J4" s="5">
+        <v>119</v>
+      </c>
+      <c r="K4" s="5">
+        <v>8</v>
+      </c>
+      <c r="L4" s="5">
+        <v>111</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.7109741981742077</v>
+      </c>
+      <c r="O4" s="5">
+        <v>1154</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1480726366312545</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1093137109403517</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1154</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.1505771420582873</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.1280034346839128</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.1728915584122243</v>
+      </c>
+      <c r="E5" s="4">
+        <v>93.36224489795917</v>
+      </c>
+      <c r="F5" s="4">
+        <v>89.79982955150734</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1260</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1065</v>
+      </c>
+      <c r="I5" s="5">
+        <v>154</v>
+      </c>
+      <c r="J5" s="5">
+        <v>41</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>40</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.08029372216439548</v>
+      </c>
+      <c r="O5" s="5">
+        <v>1065</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1380294995840084</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1012863376748737</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1065</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.183661732487953</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.1840205833169233</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.2435730046703571</v>
+      </c>
+      <c r="E6" s="4">
+        <v>93.63804832277741</v>
+      </c>
+      <c r="F6" s="4">
+        <v>93.35585898325949</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1015</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1012</v>
+      </c>
+      <c r="I6" s="5">
+        <v>3</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0.1808707514646403</v>
+      </c>
+      <c r="O6" s="5">
+        <v>1012</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.07150149319150419</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.07136287696988999</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1012</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.3521454459821016</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.350870891986996</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.467592281412627</v>
+      </c>
+      <c r="E7" s="4">
+        <v>92.3548193567412</v>
+      </c>
+      <c r="F7" s="4">
+        <v>88.47675752316685</v>
+      </c>
+      <c r="G7" s="5">
+        <v>669</v>
+      </c>
+      <c r="H7" s="5">
+        <v>575</v>
+      </c>
+      <c r="I7" s="5">
+        <v>14</v>
+      </c>
+      <c r="J7" s="5">
+        <v>80</v>
+      </c>
+      <c r="K7" s="5">
+        <v>2</v>
+      </c>
+      <c r="L7" s="5">
+        <v>78</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>0.3435723246318842</v>
+      </c>
+      <c r="O7" s="5">
+        <v>575</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.153242945396386</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1519064409343589</v>
+      </c>
+      <c r="R7" s="5">
+        <v>575</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0.2047560100984644</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.1851903673788913</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.2420165575316716</v>
+      </c>
+      <c r="E8" s="4">
+        <v>93.82634094530006</v>
+      </c>
+      <c r="F8" s="4">
+        <v>91.91591194497639</v>
+      </c>
+      <c r="G8" s="5">
+        <v>538</v>
+      </c>
+      <c r="H8" s="5">
+        <v>503</v>
+      </c>
+      <c r="I8" s="5">
+        <v>21</v>
+      </c>
+      <c r="J8" s="5">
+        <v>14</v>
+      </c>
+      <c r="K8" s="5">
+        <v>10</v>
+      </c>
+      <c r="L8" s="5">
+        <v>4</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0.1557751628083957</v>
+      </c>
+      <c r="O8" s="5">
+        <v>503</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1425538586703055</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1159361756604366</v>
+      </c>
+      <c r="R8" s="5">
+        <v>503</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>54.642166344294</v>
+      </c>
+      <c r="C3" s="3">
+        <v>17.46856866537718</v>
+      </c>
+      <c r="D3" s="3">
+        <v>27.88926499032882</v>
+      </c>
+      <c r="E3" s="3">
+        <v>10.94052224371373</v>
+      </c>
+      <c r="F3" s="3">
+        <v>16.12669245647969</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.8220502901353964</v>
+      </c>
+      <c r="H3" s="4">
+        <v>1.553629048810329</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.4765174690013938</v>
+      </c>
+      <c r="J3" s="4">
+        <v>6.595583512950965</v>
+      </c>
+      <c r="K3" s="4">
+        <v>88.95262190949883</v>
+      </c>
+      <c r="L3" s="4">
+        <v>75.54648251398757</v>
+      </c>
+      <c r="M3" s="5">
+        <v>8272</v>
+      </c>
+      <c r="N3" s="5">
+        <v>157216311.6247654</v>
+      </c>
+      <c r="O3" s="4">
+        <v>64.51215350361301</v>
+      </c>
+      <c r="P3" s="5">
+        <v>2437003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>55.58510638297872</v>
+      </c>
+      <c r="C4" s="3">
+        <v>13.63636363636363</v>
+      </c>
+      <c r="D4" s="3">
+        <v>30.77852998065764</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.5440038684719536</v>
+      </c>
+      <c r="F4" s="3">
+        <v>30.22243713733075</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.0120889748549323</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.5128732537149608</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.2992183654592619</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.4072564251273192</v>
+      </c>
+      <c r="K4" s="4">
+        <v>84.03796431532005</v>
+      </c>
+      <c r="L4" s="4">
+        <v>72.86212699968418</v>
+      </c>
+      <c r="M4" s="5">
+        <v>8272</v>
+      </c>
+      <c r="N4" s="5">
+        <v>82298466.55201912</v>
+      </c>
+      <c r="O4" s="4">
+        <v>46.56465623102108</v>
+      </c>
+      <c r="P4" s="5">
+        <v>1767402</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>71.55464216634429</v>
+      </c>
+      <c r="C5" s="3">
+        <v>13.91441005802708</v>
+      </c>
+      <c r="D5" s="3">
+        <v>14.53094777562863</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.5440038684719536</v>
+      </c>
+      <c r="F5" s="3">
+        <v>12.45164410058027</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1.535299806576402</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.5695836188461817</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.4148447884525079</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.7049243714978332</v>
+      </c>
+      <c r="K5" s="4">
+        <v>80.66818313398859</v>
+      </c>
+      <c r="L5" s="4">
+        <v>78.2277914443594</v>
+      </c>
+      <c r="M5" s="5">
+        <v>8272</v>
+      </c>
+      <c r="N5" s="5">
+        <v>165573374.4380474</v>
+      </c>
+      <c r="O5" s="4">
+        <v>118.1300027382938</v>
+      </c>
+      <c r="P5" s="5">
+        <v>1401620</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>46.01063829787234</v>
+      </c>
+      <c r="C6" s="3">
+        <v>14.96615087040619</v>
+      </c>
+      <c r="D6" s="3">
+        <v>39.02321083172147</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.2901353965183753</v>
+      </c>
+      <c r="F6" s="3">
+        <v>37.89893617021276</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.8341392649903289</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.5896877543344705</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.3934116590106763</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.8459467720802533</v>
+      </c>
+      <c r="K6" s="4">
+        <v>73.84955311911992</v>
+      </c>
+      <c r="L6" s="4">
+        <v>69.47485439140812</v>
+      </c>
+      <c r="M6" s="5">
+        <v>8272</v>
+      </c>
+      <c r="N6" s="5">
+        <v>238741497.8296757</v>
+      </c>
+      <c r="O6" s="4">
+        <v>111.3509734309101</v>
+      </c>
+      <c r="P6" s="5">
+        <v>2144045</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>94.34235976789168</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2.599129593810445</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3.058510638297872</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.1571566731141199</v>
+      </c>
+      <c r="F7" s="3">
+        <v>2.901353965183752</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.1331244190821007</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.1083673926442958</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.1134765612977554</v>
+      </c>
+      <c r="K7" s="4">
+        <v>96.86285345859815</v>
+      </c>
+      <c r="L7" s="4">
+        <v>93.91545668739369</v>
+      </c>
+      <c r="M7" s="5">
+        <v>8272</v>
+      </c>
+      <c r="N7" s="5">
+        <v>226840232.2740555</v>
+      </c>
+      <c r="O7" s="4">
+        <v>399.779758789551</v>
+      </c>
+      <c r="P7" s="5">
+        <v>567413</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>74.08123791102514</v>
+      </c>
+      <c r="C8" s="3">
+        <v>15.63104448742747</v>
+      </c>
+      <c r="D8" s="3">
+        <v>10.28771760154739</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.1813346228239845</v>
+      </c>
+      <c r="F8" s="3">
+        <v>9.888781431334623</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.2176015473887814</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.4349410797668186</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.3630958323038463</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.5235608809339586</v>
+      </c>
+      <c r="K8" s="4">
+        <v>91.05157222463453</v>
+      </c>
+      <c r="L8" s="4">
+        <v>83.76394288811285</v>
+      </c>
+      <c r="M8" s="5">
+        <v>8272</v>
+      </c>
+      <c r="N8" s="5">
+        <v>30020933.71582031</v>
+      </c>
+      <c r="O8" s="4">
+        <v>30.04322578935601</v>
+      </c>
+      <c r="P8" s="5">
+        <v>999258</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>46.31286266924565</v>
+      </c>
+      <c r="C9" s="3">
+        <v>7.990812379110252</v>
+      </c>
+      <c r="D9" s="3">
+        <v>45.6963249516441</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.5681818181818182</v>
+      </c>
+      <c r="F9" s="3">
+        <v>43.44777562862669</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1.68036750483559</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.7045639802562231</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.3693776638527504</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.9925033604158195</v>
+      </c>
+      <c r="K9" s="4">
+        <v>79.75043257148117</v>
+      </c>
+      <c r="L9" s="4">
+        <v>70.92996129364488</v>
+      </c>
+      <c r="M9" s="5">
+        <v>8272</v>
+      </c>
+      <c r="N9" s="5">
+        <v>63685522.04585075</v>
+      </c>
+      <c r="O9" s="4">
+        <v>42.62800985409523</v>
+      </c>
+      <c r="P9" s="5">
+        <v>1493983</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>85.52949709864603</v>
+      </c>
+      <c r="C10" s="3">
+        <v>7.229206963249517</v>
+      </c>
+      <c r="D10" s="3">
+        <v>7.241295938104448</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.4110251450676982</v>
+      </c>
+      <c r="F10" s="3">
+        <v>6.370889748549323</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.4593810444874275</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.376665153874602</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.3070952308666277</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.4161477512154155</v>
+      </c>
+      <c r="K10" s="4">
+        <v>89.24772447663777</v>
+      </c>
+      <c r="L10" s="4">
+        <v>85.55428084933288</v>
+      </c>
+      <c r="M10" s="5">
+        <v>8272</v>
+      </c>
+      <c r="N10" s="5">
+        <v>99576115.5025959</v>
+      </c>
+      <c r="O10" s="4">
+        <v>97.39600336331154</v>
+      </c>
+      <c r="P10" s="5">
+        <v>1022384</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>57.79738878143134</v>
+      </c>
+      <c r="C11" s="3">
+        <v>19.37862669245648</v>
+      </c>
+      <c r="D11" s="3">
+        <v>22.82398452611218</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.8945841392649904</v>
+      </c>
+      <c r="F11" s="3">
+        <v>21.69970986460348</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.2296905222437138</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.5371953346161347</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.319788967772593</v>
+      </c>
+      <c r="J11" s="4">
+        <v>1.458949107525936</v>
+      </c>
+      <c r="K11" s="4">
+        <v>88.62407317859473</v>
+      </c>
+      <c r="L11" s="4">
+        <v>77.20586604658619</v>
+      </c>
+      <c r="M11" s="5">
+        <v>8272</v>
+      </c>
+      <c r="N11" s="5">
+        <v>79503380.49173355</v>
+      </c>
+      <c r="O11" s="4">
+        <v>65.08742670135683</v>
+      </c>
+      <c r="P11" s="5">
+        <v>1221486</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>71.36121856866538</v>
+      </c>
+      <c r="C12" s="3">
+        <v>15.09912959381045</v>
+      </c>
+      <c r="D12" s="3">
+        <v>13.53965183752418</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.6890715667311412</v>
+      </c>
+      <c r="F12" s="3">
+        <v>12.54835589941973</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.3022243713733075</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.4580614647594063</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.3324800109203493</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1.243584896379664</v>
+      </c>
+      <c r="K12" s="4">
+        <v>88.57734559007346</v>
+      </c>
+      <c r="L12" s="4">
+        <v>82.34633209144137</v>
+      </c>
+      <c r="M12" s="5">
+        <v>8272</v>
+      </c>
+      <c r="N12" s="5">
+        <v>69215846.16398811</v>
+      </c>
+      <c r="O12" s="4">
+        <v>59.44688079591466</v>
+      </c>
+      <c r="P12" s="5">
+        <v>1164331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>79.53336557059961</v>
+      </c>
+      <c r="C13" s="3">
+        <v>9.973404255319149</v>
+      </c>
+      <c r="D13" s="3">
+        <v>10.49323017408124</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.5077369439071566</v>
+      </c>
+      <c r="F13" s="3">
+        <v>9.272243713733076</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.7132495164410058</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.4643011816676134</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.4026441827348264</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.5389741241323918</v>
+      </c>
+      <c r="K13" s="4">
+        <v>86.69234957038906</v>
+      </c>
+      <c r="L13" s="4">
+        <v>83.03112518877191</v>
+      </c>
+      <c r="M13" s="5">
+        <v>8272</v>
+      </c>
+      <c r="N13" s="5">
+        <v>43666445.92142105</v>
+      </c>
+      <c r="O13" s="4">
+        <v>37.87517947844838</v>
+      </c>
+      <c r="P13" s="5">
+        <v>1152904</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>54.06189555125726</v>
+      </c>
+      <c r="C14" s="3">
+        <v>12.52417794970986</v>
+      </c>
+      <c r="D14" s="3">
+        <v>33.41392649903288</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2.381528046421664</v>
+      </c>
+      <c r="F14" s="3">
+        <v>30.68181818181818</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.3505802707930368</v>
+      </c>
+      <c r="H14" s="4">
+        <v>1.054561822527934</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.3910191458821542</v>
+      </c>
+      <c r="J14" s="4">
+        <v>2.180793732473049</v>
+      </c>
+      <c r="K14" s="4">
+        <v>85.87513487019545</v>
+      </c>
+      <c r="L14" s="4">
+        <v>73.38831247647126</v>
+      </c>
+      <c r="M14" s="5">
+        <v>8272</v>
+      </c>
+      <c r="N14" s="5">
+        <v>126510471.0562229</v>
+      </c>
+      <c r="O14" s="4">
+        <v>76.73947379653222</v>
+      </c>
+      <c r="P14" s="5">
+        <v>1648571</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>57.70067698259188</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.8945841392649904</v>
+      </c>
+      <c r="D15" s="3">
+        <v>41.40473887814314</v>
+      </c>
+      <c r="E15" s="3">
+        <v>40.2321083172147</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1.160541586073501</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.0120889748549323</v>
+      </c>
+      <c r="H15" s="4">
+        <v>1.065805680520617</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.07787302540479989</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.5059381596407519</v>
+      </c>
+      <c r="K15" s="4">
+        <v>95.71748065764029</v>
+      </c>
+      <c r="L15" s="4">
+        <v>93.14509149758305</v>
+      </c>
+      <c r="M15" s="5">
+        <v>8272</v>
+      </c>
+      <c r="N15" s="5">
+        <v>387370485.9704971</v>
+      </c>
+      <c r="O15" s="4">
+        <v>540.2875234430641</v>
+      </c>
+      <c r="P15" s="5">
+        <v>716971</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>95.07978723404256</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2.357350096711799</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2.562862669245648</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.04835589941972921</v>
+      </c>
+      <c r="F16" s="3">
+        <v>2.514506769825918</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.1281250395780686</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.1078197905373326</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.1754669240497785</v>
+      </c>
+      <c r="K16" s="4">
+        <v>89.95696489427473</v>
+      </c>
+      <c r="L16" s="4">
+        <v>90.51687399123344</v>
+      </c>
+      <c r="M16" s="5">
+        <v>8272</v>
+      </c>
+      <c r="N16" s="5">
+        <v>466421241.2323952</v>
+      </c>
+      <c r="O16" s="4">
+        <v>533.3460350574375</v>
+      </c>
+      <c r="P16" s="5">
+        <v>874519</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>85.08220502901354</v>
+      </c>
+      <c r="C17" s="3">
+        <v>8.776595744680851</v>
+      </c>
+      <c r="D17" s="3">
+        <v>6.141199226305609</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.4231141199226305</v>
+      </c>
+      <c r="F17" s="3">
+        <v>5.645551257253385</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.07253384912959382</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.2627155627044335</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.2089793513210562</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.2791479264438044</v>
+      </c>
+      <c r="K17" s="4">
+        <v>92.25240216976553</v>
+      </c>
+      <c r="L17" s="4">
+        <v>88.83323678380262</v>
+      </c>
+      <c r="M17" s="5">
+        <v>8272</v>
+      </c>
+      <c r="N17" s="5">
+        <v>128505693.6891079</v>
+      </c>
+      <c r="O17" s="4">
+        <v>131.2836558468267</v>
+      </c>
+      <c r="P17" s="5">
+        <v>978840</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="25" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="3">
+        <v>88.23742746615088</v>
+      </c>
+      <c r="C18" s="3">
+        <v>5.718085106382978</v>
+      </c>
+      <c r="D18" s="3">
+        <v>6.044487427466152</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.08462282398452611</v>
+      </c>
+      <c r="F18" s="3">
+        <v>5.863152804642166</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0.09671179883945842</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0.3142637197174933</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0.2834355298932507</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0.3181071164546737</v>
+      </c>
+      <c r="K18" s="4">
+        <v>90.66779250384869</v>
+      </c>
+      <c r="L18" s="4">
+        <v>88.60384645757911</v>
+      </c>
+      <c r="M18" s="5">
+        <v>8272</v>
+      </c>
+      <c r="N18" s="5">
+        <v>175359670.337677</v>
+      </c>
+      <c r="O18" s="4">
+        <v>109.7824445030901</v>
+      </c>
+      <c r="P18" s="5">
+        <v>1597338</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1.036238909405371</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.9731148121978462</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1.120655116299837</v>
+      </c>
+      <c r="E3" s="4">
+        <v>90.35276689472352</v>
+      </c>
+      <c r="F3" s="4">
+        <v>87.29020275251118</v>
+      </c>
+      <c r="G3" s="5">
+        <v>3490</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2527</v>
+      </c>
+      <c r="I3" s="5">
+        <v>397</v>
+      </c>
+      <c r="J3" s="5">
+        <v>566</v>
+      </c>
+      <c r="K3" s="5">
+        <v>5</v>
+      </c>
+      <c r="L3" s="5">
+        <v>395</v>
+      </c>
+      <c r="M3" s="5">
+        <v>166</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1.016763890508596</v>
+      </c>
+      <c r="O3" s="5">
+        <v>2693</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5296837558775771</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5162387356018742</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2685</v>
+      </c>
+      <c r="S3" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4834003091289333</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.4858857864286872</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.5373773054569767</v>
+      </c>
+      <c r="E4" s="4">
+        <v>90.79246467817897</v>
+      </c>
+      <c r="F4" s="4">
+        <v>89.6296764756493</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1300</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1259</v>
+      </c>
+      <c r="I4" s="5">
+        <v>10</v>
+      </c>
+      <c r="J4" s="5">
+        <v>31</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>30</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.4849976781787187</v>
+      </c>
+      <c r="O4" s="5">
+        <v>1259</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1744290408941523</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.173219810382425</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1259</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.1518970015853073</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.1309823756418455</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.1281928934472783</v>
+      </c>
+      <c r="E5" s="4">
+        <v>90.94374257639566</v>
+      </c>
+      <c r="F5" s="4">
+        <v>88.98646177337439</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1260</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1185</v>
+      </c>
+      <c r="I5" s="5">
+        <v>53</v>
+      </c>
+      <c r="J5" s="5">
+        <v>22</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>22</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.0332075817416683</v>
+      </c>
+      <c r="O5" s="5">
+        <v>1185</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1470990085152149</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1278628783994427</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1185</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.1881001581961826</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.1881623030204206</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.1955659717746267</v>
+      </c>
+      <c r="E6" s="4">
+        <v>90.95693844040079</v>
+      </c>
+      <c r="F6" s="4">
+        <v>90.49177328881113</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1015</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1011</v>
+      </c>
+      <c r="I6" s="5">
+        <v>2</v>
+      </c>
+      <c r="J6" s="5">
+        <v>2</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>2</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>-0.08634435159529383</v>
+      </c>
+      <c r="O6" s="5">
+        <v>1011</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1731168995311282</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.173092831521953</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1011</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.1564620508023996</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.1303017611922076</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.1583719914497226</v>
+      </c>
+      <c r="E7" s="4">
+        <v>90.4063837792217</v>
+      </c>
+      <c r="F7" s="4">
+        <v>87.95586253482045</v>
+      </c>
+      <c r="G7" s="5">
+        <v>669</v>
+      </c>
+      <c r="H7" s="5">
+        <v>632</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>37</v>
+      </c>
+      <c r="K7" s="5">
+        <v>1</v>
+      </c>
+      <c r="L7" s="5">
+        <v>36</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>-0.06724703260005652</v>
+      </c>
+      <c r="O7" s="5">
+        <v>632</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1399964199342545</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1165962850691267</v>
+      </c>
+      <c r="R7" s="5">
+        <v>632</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0.1429144716529124</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.1376156927300987</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.1506999249734916</v>
+      </c>
+      <c r="E8" s="4">
+        <v>91.54338315251751</v>
+      </c>
+      <c r="F8" s="4">
+        <v>90.99454853920673</v>
+      </c>
+      <c r="G8" s="5">
+        <v>538</v>
+      </c>
+      <c r="H8" s="5">
+        <v>527</v>
+      </c>
+      <c r="I8" s="5">
+        <v>11</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0.06790303323325575</v>
+      </c>
+      <c r="O8" s="5">
+        <v>527</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1292182521165063</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1222162629840792</v>
+      </c>
+      <c r="R8" s="5">
+        <v>527</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4589,10 +7736,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>259</v>
+        <v>110</v>
       </c>
       <c r="L3" s="5">
-        <v>1741</v>
+        <v>1232</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
@@ -4633,10 +7780,10 @@
         <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="L4" s="5">
-        <v>2316</v>
+        <v>2291</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
@@ -4677,16 +7824,16 @@
         <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
-        <v>938</v>
+        <v>919</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
       <c r="N5" s="5">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="25" customHeight="1">
@@ -4721,16 +7868,16 @@
         <v>0</v>
       </c>
       <c r="K6" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L6" s="5">
-        <v>3100</v>
+        <v>3082</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
       <c r="N6" s="5">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="25" customHeight="1">
@@ -4765,10 +7912,10 @@
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="L7" s="5">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
@@ -4809,10 +7956,10 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L8" s="5">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
@@ -4853,16 +8000,16 @@
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="L9" s="5">
-        <v>3400</v>
+        <v>3365</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
       </c>
       <c r="N9" s="5">
-        <v>1434</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25" customHeight="1">
@@ -4897,10 +8044,10 @@
         <v>0</v>
       </c>
       <c r="K10" s="5">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="L10" s="5">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
@@ -4941,16 +8088,16 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="L11" s="5">
-        <v>1715</v>
+        <v>1676</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
       </c>
       <c r="N11" s="5">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="25" customHeight="1">
@@ -4985,10 +8132,10 @@
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="L12" s="5">
-        <v>1052</v>
+        <v>1024</v>
       </c>
       <c r="M12" s="5">
         <v>0</v>
@@ -5029,10 +8176,10 @@
         <v>0</v>
       </c>
       <c r="K13" s="5">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="L13" s="5">
-        <v>782</v>
+        <v>763</v>
       </c>
       <c r="M13" s="5">
         <v>0</v>
@@ -5073,10 +8220,10 @@
         <v>0</v>
       </c>
       <c r="K14" s="5">
-        <v>112</v>
+        <v>35</v>
       </c>
       <c r="L14" s="5">
-        <v>2680</v>
+        <v>2526</v>
       </c>
       <c r="M14" s="5">
         <v>0</v>
@@ -5117,10 +8264,10 @@
         <v>0</v>
       </c>
       <c r="K15" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L15" s="5">
-        <v>216</v>
+        <v>95</v>
       </c>
       <c r="M15" s="5">
         <v>0</v>
@@ -5164,7 +8311,7 @@
         <v>6</v>
       </c>
       <c r="L16" s="5">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M16" s="5">
         <v>0</v>
@@ -5205,10 +8352,10 @@
         <v>0</v>
       </c>
       <c r="K17" s="5">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="L17" s="5">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="M17" s="5">
         <v>0</v>
@@ -5249,13 +8396,13 @@
         <v>0</v>
       </c>
       <c r="K18" s="5">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L18" s="5">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="M18" s="5">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N18" s="5">
         <v>0</v>
@@ -5274,9 +8421,808 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>4520</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1445</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2307</v>
+      </c>
+      <c r="E3" s="5">
+        <v>905</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1334</v>
+      </c>
+      <c r="G3" s="5">
+        <v>68</v>
+      </c>
+      <c r="H3" s="5">
+        <v>905</v>
+      </c>
+      <c r="I3" s="5">
+        <v>905</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>110</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1232</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>4598</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1128</v>
+      </c>
+      <c r="D4" s="5">
+        <v>2546</v>
+      </c>
+      <c r="E4" s="5">
+        <v>45</v>
+      </c>
+      <c r="F4" s="5">
+        <v>2500</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>45</v>
+      </c>
+      <c r="I4" s="5">
+        <v>45</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>68</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2291</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>5919</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1151</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1202</v>
+      </c>
+      <c r="E5" s="5">
+        <v>45</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1030</v>
+      </c>
+      <c r="G5" s="5">
+        <v>127</v>
+      </c>
+      <c r="H5" s="5">
+        <v>45</v>
+      </c>
+      <c r="I5" s="5">
+        <v>45</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>2</v>
+      </c>
+      <c r="L5" s="5">
+        <v>919</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>3806</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1238</v>
+      </c>
+      <c r="D6" s="5">
+        <v>3228</v>
+      </c>
+      <c r="E6" s="5">
+        <v>24</v>
+      </c>
+      <c r="F6" s="5">
+        <v>3135</v>
+      </c>
+      <c r="G6" s="5">
+        <v>69</v>
+      </c>
+      <c r="H6" s="5">
+        <v>24</v>
+      </c>
+      <c r="I6" s="5">
+        <v>24</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>2</v>
+      </c>
+      <c r="L6" s="5">
+        <v>3082</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>7804</v>
+      </c>
+      <c r="C7" s="5">
+        <v>215</v>
+      </c>
+      <c r="D7" s="5">
+        <v>253</v>
+      </c>
+      <c r="E7" s="5">
+        <v>13</v>
+      </c>
+      <c r="F7" s="5">
+        <v>240</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>13</v>
+      </c>
+      <c r="I7" s="5">
+        <v>13</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>2</v>
+      </c>
+      <c r="L7" s="5">
+        <v>238</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>6128</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1293</v>
+      </c>
+      <c r="D8" s="5">
+        <v>851</v>
+      </c>
+      <c r="E8" s="5">
+        <v>15</v>
+      </c>
+      <c r="F8" s="5">
+        <v>818</v>
+      </c>
+      <c r="G8" s="5">
+        <v>18</v>
+      </c>
+      <c r="H8" s="5">
+        <v>15</v>
+      </c>
+      <c r="I8" s="5">
+        <v>15</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>7</v>
+      </c>
+      <c r="L8" s="5">
+        <v>811</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>3831</v>
+      </c>
+      <c r="C9" s="5">
+        <v>661</v>
+      </c>
+      <c r="D9" s="5">
+        <v>3780</v>
+      </c>
+      <c r="E9" s="5">
+        <v>47</v>
+      </c>
+      <c r="F9" s="5">
+        <v>3594</v>
+      </c>
+      <c r="G9" s="5">
+        <v>139</v>
+      </c>
+      <c r="H9" s="5">
+        <v>47</v>
+      </c>
+      <c r="I9" s="5">
+        <v>47</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>4</v>
+      </c>
+      <c r="L9" s="5">
+        <v>3365</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>7075</v>
+      </c>
+      <c r="C10" s="5">
+        <v>598</v>
+      </c>
+      <c r="D10" s="5">
+        <v>599</v>
+      </c>
+      <c r="E10" s="5">
+        <v>34</v>
+      </c>
+      <c r="F10" s="5">
+        <v>527</v>
+      </c>
+      <c r="G10" s="5">
+        <v>38</v>
+      </c>
+      <c r="H10" s="5">
+        <v>34</v>
+      </c>
+      <c r="I10" s="5">
+        <v>34</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>5</v>
+      </c>
+      <c r="L10" s="5">
+        <v>522</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>4781</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1603</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1888</v>
+      </c>
+      <c r="E11" s="5">
+        <v>74</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1795</v>
+      </c>
+      <c r="G11" s="5">
+        <v>19</v>
+      </c>
+      <c r="H11" s="5">
+        <v>74</v>
+      </c>
+      <c r="I11" s="5">
+        <v>74</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>13</v>
+      </c>
+      <c r="L11" s="5">
+        <v>1676</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>5903</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1249</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1120</v>
+      </c>
+      <c r="E12" s="5">
+        <v>57</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1038</v>
+      </c>
+      <c r="G12" s="5">
+        <v>25</v>
+      </c>
+      <c r="H12" s="5">
+        <v>57</v>
+      </c>
+      <c r="I12" s="5">
+        <v>57</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>14</v>
+      </c>
+      <c r="L12" s="5">
+        <v>1024</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>6579</v>
+      </c>
+      <c r="C13" s="5">
+        <v>825</v>
+      </c>
+      <c r="D13" s="5">
+        <v>868</v>
+      </c>
+      <c r="E13" s="5">
+        <v>42</v>
+      </c>
+      <c r="F13" s="5">
+        <v>767</v>
+      </c>
+      <c r="G13" s="5">
+        <v>59</v>
+      </c>
+      <c r="H13" s="5">
+        <v>42</v>
+      </c>
+      <c r="I13" s="5">
+        <v>42</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>4</v>
+      </c>
+      <c r="L13" s="5">
+        <v>763</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>4472</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1036</v>
+      </c>
+      <c r="D14" s="5">
+        <v>2764</v>
+      </c>
+      <c r="E14" s="5">
+        <v>197</v>
+      </c>
+      <c r="F14" s="5">
+        <v>2538</v>
+      </c>
+      <c r="G14" s="5">
+        <v>29</v>
+      </c>
+      <c r="H14" s="5">
+        <v>197</v>
+      </c>
+      <c r="I14" s="5">
+        <v>197</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>35</v>
+      </c>
+      <c r="L14" s="5">
+        <v>2526</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>4773</v>
+      </c>
+      <c r="C15" s="5">
+        <v>74</v>
+      </c>
+      <c r="D15" s="5">
+        <v>3425</v>
+      </c>
+      <c r="E15" s="5">
+        <v>3328</v>
+      </c>
+      <c r="F15" s="5">
+        <v>96</v>
+      </c>
+      <c r="G15" s="5">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5">
+        <v>3326</v>
+      </c>
+      <c r="I15" s="5">
+        <v>15</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>1</v>
+      </c>
+      <c r="L15" s="5">
+        <v>95</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>7865</v>
+      </c>
+      <c r="C16" s="5">
+        <v>195</v>
+      </c>
+      <c r="D16" s="5">
+        <v>212</v>
+      </c>
+      <c r="E16" s="5">
+        <v>4</v>
+      </c>
+      <c r="F16" s="5">
+        <v>208</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>4</v>
+      </c>
+      <c r="I16" s="5">
+        <v>4</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>6</v>
+      </c>
+      <c r="L16" s="5">
+        <v>203</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>7038</v>
+      </c>
+      <c r="C17" s="5">
+        <v>726</v>
+      </c>
+      <c r="D17" s="5">
+        <v>508</v>
+      </c>
+      <c r="E17" s="5">
+        <v>35</v>
+      </c>
+      <c r="F17" s="5">
+        <v>467</v>
+      </c>
+      <c r="G17" s="5">
+        <v>6</v>
+      </c>
+      <c r="H17" s="5">
+        <v>35</v>
+      </c>
+      <c r="I17" s="5">
+        <v>35</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>12</v>
+      </c>
+      <c r="L17" s="5">
+        <v>455</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="25" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="5">
+        <v>7299</v>
+      </c>
+      <c r="C18" s="5">
+        <v>473</v>
+      </c>
+      <c r="D18" s="5">
+        <v>500</v>
+      </c>
+      <c r="E18" s="5">
+        <v>7</v>
+      </c>
+      <c r="F18" s="5">
+        <v>485</v>
+      </c>
+      <c r="G18" s="5">
+        <v>8</v>
+      </c>
+      <c r="H18" s="5">
+        <v>7</v>
+      </c>
+      <c r="I18" s="5">
+        <v>7</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5">
+        <v>10</v>
+      </c>
+      <c r="L18" s="5">
+        <v>270</v>
+      </c>
+      <c r="M18" s="5">
+        <v>210</v>
+      </c>
+      <c r="N18" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5287,9 +9233,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -5323,8 +9275,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5346,10 +9306,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>1.127461105997826</v>
@@ -5387,17 +9365,33 @@
       <c r="M3" s="5">
         <v>385</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.9479253781350711</v>
+      </c>
+      <c r="O3" s="5">
+        <v>2531</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7946853260850163</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7459435568170002</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2463</v>
+      </c>
+      <c r="S3" s="5">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>6.917093716917519</v>
       </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
         <v>26.59489508298585</v>
       </c>
@@ -5428,17 +9422,29 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>6.917093716917519</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>0.5751060548741748</v>
       </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
         <v>13.03758841852848</v>
       </c>
@@ -5469,10 +9475,24 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5751060548741748</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.5853192485273805</v>
@@ -5510,10 +9530,28 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.5842797136229048</v>
+      </c>
+      <c r="O6" s="5">
+        <v>1011</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1654131969162824</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1654931407345905</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1011</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>0.3895262027717925</v>
@@ -5551,10 +9589,28 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.3593939146418442</v>
+      </c>
+      <c r="O7" s="5">
+        <v>517</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1994982680708965</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1849756045652493</v>
+      </c>
+      <c r="R7" s="5">
+        <v>517</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.177877292297926</v>
@@ -5592,9 +9648,27 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>-0.1416358040285098</v>
+      </c>
+      <c r="O8" s="5">
+        <v>529</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1114377441982315</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1014253811023138</v>
+      </c>
+      <c r="R8" s="5">
+        <v>529</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5605,14 +9679,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5623,9 +9698,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -5659,8 +9740,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5682,10 +9771,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>1.307543660456592</v>
@@ -5723,10 +9830,28 @@
       <c r="M3" s="5">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.751817093973262</v>
+      </c>
+      <c r="O3" s="5">
+        <v>1221</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8166344676950249</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4352143445214753</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1220</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.5129352577454734</v>
@@ -5764,10 +9889,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.4779520507839981</v>
+      </c>
+      <c r="O4" s="5">
+        <v>997</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2911926697603702</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2665245382373198</v>
+      </c>
+      <c r="R4" s="5">
+        <v>997</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>1.635352757263416</v>
@@ -5805,10 +9948,28 @@
       <c r="M5" s="5">
         <v>34</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-1.477040555650098</v>
+      </c>
+      <c r="O5" s="5">
+        <v>470</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2832180902445739</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2260394299862759</v>
+      </c>
+      <c r="R5" s="5">
+        <v>470</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.4197822782434587</v>
@@ -5846,10 +10007,28 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.4008128083953016</v>
+      </c>
+      <c r="O6" s="5">
+        <v>976</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2295752883988079</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2250716892318951</v>
+      </c>
+      <c r="R6" s="5">
+        <v>976</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>1.314880911052612</v>
@@ -5887,10 +10066,28 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-1.136406884444126</v>
+      </c>
+      <c r="O7" s="5">
+        <v>433</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.5105877536042301</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.4185847535913781</v>
+      </c>
+      <c r="R7" s="5">
+        <v>433</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.6027986149197437</v>
@@ -5928,9 +10125,27 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>-0.5928337898476563</v>
+      </c>
+      <c r="O8" s="5">
+        <v>502</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1532079427357905</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1433543433345275</v>
+      </c>
+      <c r="R8" s="5">
+        <v>502</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5941,14 +10156,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5959,9 +10175,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -5995,8 +10217,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -6018,10 +10248,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>1.48067253553555</v>
@@ -6059,10 +10307,28 @@
       <c r="M3" s="5">
         <v>474</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>1.310281669241787</v>
+      </c>
+      <c r="O3" s="5">
+        <v>1698</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.967751480212575</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.8329146192916319</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1571</v>
+      </c>
+      <c r="S3" s="5">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.4248418557581993</v>
@@ -6100,10 +10366,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.4360050519184081</v>
+      </c>
+      <c r="O4" s="5">
+        <v>1101</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3369712888137829</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3049127242381223</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1101</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>0.4808518477791844</v>
@@ -6141,10 +10425,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.4450389279639529</v>
+      </c>
+      <c r="O5" s="5">
+        <v>1225</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3730970025908129</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3575160263912761</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1225</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.7034656838027977</v>
@@ -6182,10 +10484,28 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.6945662180134372</v>
+      </c>
+      <c r="O6" s="5">
+        <v>988</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1413821884771314</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1352276166132494</v>
+      </c>
+      <c r="R6" s="5">
+        <v>988</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>0.4308985611149814</v>
@@ -6223,10 +10543,28 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.4155674305653763</v>
+      </c>
+      <c r="O7" s="5">
+        <v>572</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1713432011405112</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1655138918160258</v>
+      </c>
+      <c r="R7" s="5">
+        <v>572</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.3056486170737047</v>
@@ -6264,9 +10602,27 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>-0.1824044946025602</v>
+      </c>
+      <c r="O8" s="5">
+        <v>462</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.3119825419406986</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.3138800062664451</v>
+      </c>
+      <c r="R8" s="5">
+        <v>462</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -6277,14 +10633,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -6295,9 +10652,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -6331,8 +10694,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -6354,10 +10725,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>1.744817717780426</v>
@@ -6395,10 +10784,28 @@
       <c r="M3" s="5">
         <v>376</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>1.661851415947627</v>
+      </c>
+      <c r="O3" s="5">
+        <v>1078</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.9336646200640316</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7912223317544755</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1010</v>
+      </c>
+      <c r="S3" s="5">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.3340549933499001</v>
@@ -6436,10 +10843,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1642673449767935</v>
+      </c>
+      <c r="O4" s="5">
+        <v>827</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2547537685432583</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1832291423578742</v>
+      </c>
+      <c r="R4" s="5">
+        <v>827</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>1.003346345422901</v>
@@ -6477,10 +10902,28 @@
       <c r="M5" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.6365731433972929</v>
+      </c>
+      <c r="O5" s="5">
+        <v>369</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4657269221169018</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2564209718789762</v>
+      </c>
+      <c r="R5" s="5">
+        <v>368</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.9047333469350026</v>
@@ -6518,10 +10961,28 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.8416015685477901</v>
+      </c>
+      <c r="O6" s="5">
+        <v>813</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2634840054410612</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2393829555059815</v>
+      </c>
+      <c r="R6" s="5">
+        <v>813</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>1.266396990753177</v>
@@ -6559,10 +11020,28 @@
       <c r="M7" s="5">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-1.212999258774814</v>
+      </c>
+      <c r="O7" s="5">
+        <v>417</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.4252692823776592</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.4268955579724044</v>
+      </c>
+      <c r="R7" s="5">
+        <v>417</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.4663601434537136</v>
@@ -6600,9 +11079,27 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>-0.3494381451147357</v>
+      </c>
+      <c r="O8" s="5">
+        <v>371</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.2778259171457356</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.21472509498742</v>
+      </c>
+      <c r="R8" s="5">
+        <v>371</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -6613,14 +11110,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -6631,9 +11129,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -6667,8 +11171,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -6690,10 +11202,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.262493390427208</v>
@@ -6731,10 +11261,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1923855028290324</v>
+      </c>
+      <c r="O3" s="5">
+        <v>3183</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1780017278864942</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.138284630938787</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3183</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>0.8702271365877036</v>
@@ -6772,10 +11320,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.8691649302660104</v>
+      </c>
+      <c r="O4" s="5">
+        <v>1269</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.07265224155654214</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06821051062798039</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1269</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>0.1547609513450279</v>
@@ -6813,10 +11379,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>0.02871901425934644</v>
+      </c>
+      <c r="O5" s="5">
+        <v>1168</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1583729775831024</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1262864014173563</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1168</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>0.112879419965108</v>
@@ -6854,10 +11438,28 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>0.1060807015136412</v>
+      </c>
+      <c r="O6" s="5">
+        <v>1013</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.07155580986101853</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.0713980367447246</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1013</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>0.1223689511217986</v>
@@ -6895,10 +11497,28 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.02382147472023172</v>
+      </c>
+      <c r="O7" s="5">
+        <v>640</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1169463679825334</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.104735587769052</v>
+      </c>
+      <c r="R7" s="5">
+        <v>640</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>0.06726725427944522</v>
@@ -6936,9 +11556,27 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>0.02605915424773427</v>
+      </c>
+      <c r="O8" s="5">
+        <v>531</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.0652695750107975</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.0604906020356813</v>
+      </c>
+      <c r="R8" s="5">
+        <v>531</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -6949,678 +11587,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.9688806581149634</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.9077242341395307</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.433518686758558</v>
-      </c>
-      <c r="E3" s="4">
-        <v>89.28797536206457</v>
-      </c>
-      <c r="F3" s="4">
-        <v>82.00563130196262</v>
-      </c>
-      <c r="G3" s="5">
-        <v>3490</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1948</v>
-      </c>
-      <c r="I3" s="5">
-        <v>951</v>
-      </c>
-      <c r="J3" s="5">
-        <v>591</v>
-      </c>
-      <c r="K3" s="5">
-        <v>8</v>
-      </c>
-      <c r="L3" s="5">
-        <v>397</v>
-      </c>
-      <c r="M3" s="5">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1.626381551450666</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1.573717270044479</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1.859486304924868</v>
-      </c>
-      <c r="E4" s="4">
-        <v>92.19374672946101</v>
-      </c>
-      <c r="F4" s="4">
-        <v>85.37032352435013</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1300</v>
-      </c>
-      <c r="H4" s="5">
-        <v>772</v>
-      </c>
-      <c r="I4" s="5">
-        <v>31</v>
-      </c>
-      <c r="J4" s="5">
-        <v>497</v>
-      </c>
-      <c r="K4" s="5">
-        <v>3</v>
-      </c>
-      <c r="L4" s="5">
-        <v>220</v>
-      </c>
-      <c r="M4" s="5">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.379929596218835</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.4095374063859065</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3320893475605322</v>
-      </c>
-      <c r="E5" s="4">
-        <v>92.14947089947093</v>
-      </c>
-      <c r="F5" s="4">
-        <v>82.3759720890594</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1260</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1027</v>
-      </c>
-      <c r="I5" s="5">
-        <v>206</v>
-      </c>
-      <c r="J5" s="5">
-        <v>27</v>
-      </c>
-      <c r="K5" s="5">
-        <v>3</v>
-      </c>
-      <c r="L5" s="5">
-        <v>24</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.641312479962494</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.6348324158098404</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.4643216367702424</v>
-      </c>
-      <c r="E6" s="4">
-        <v>92.75158339197748</v>
-      </c>
-      <c r="F6" s="4">
-        <v>88.02086157304802</v>
-      </c>
-      <c r="G6" s="5">
-        <v>1015</v>
-      </c>
-      <c r="H6" s="5">
-        <v>976</v>
-      </c>
-      <c r="I6" s="5">
-        <v>29</v>
-      </c>
-      <c r="J6" s="5">
-        <v>10</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>10</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.5922682712079942</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0.5314704069337181</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.2607375434064936</v>
-      </c>
-      <c r="E7" s="4">
-        <v>91.31402336719439</v>
-      </c>
-      <c r="F7" s="4">
-        <v>82.70086576178083</v>
-      </c>
-      <c r="G7" s="5">
-        <v>669</v>
-      </c>
-      <c r="H7" s="5">
-        <v>499</v>
-      </c>
-      <c r="I7" s="5">
-        <v>13</v>
-      </c>
-      <c r="J7" s="5">
-        <v>157</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>157</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="4">
-        <v>0.2409181859402017</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0.1871982201257406</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0.2236282857700216</v>
-      </c>
-      <c r="E8" s="4">
-        <v>93.62719065321296</v>
-      </c>
-      <c r="F8" s="4">
-        <v>87.8298944637108</v>
-      </c>
-      <c r="G8" s="5">
-        <v>538</v>
-      </c>
-      <c r="H8" s="5">
-        <v>464</v>
-      </c>
-      <c r="I8" s="5">
-        <v>63</v>
-      </c>
-      <c r="J8" s="5">
-        <v>11</v>
-      </c>
-      <c r="K8" s="5">
-        <v>1</v>
-      </c>
-      <c r="L8" s="5">
-        <v>10</v>
-      </c>
-      <c r="M8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="4">
-        <v>2.728989691339296</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1.11393331567318</v>
-      </c>
-      <c r="D3" s="4">
-        <v>3.758038630237912</v>
-      </c>
-      <c r="E3" s="4">
-        <v>75.12162056799801</v>
-      </c>
-      <c r="F3" s="4">
-        <v>64.97866066678203</v>
-      </c>
-      <c r="G3" s="5">
-        <v>3490</v>
-      </c>
-      <c r="H3" s="5">
-        <v>430</v>
-      </c>
-      <c r="I3" s="5">
-        <v>541</v>
-      </c>
-      <c r="J3" s="5">
-        <v>2519</v>
-      </c>
-      <c r="K3" s="5">
-        <v>39</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1941</v>
-      </c>
-      <c r="M3" s="5">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2451883431170309</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2349038390628152</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3363890841250518</v>
-      </c>
-      <c r="E4" s="4">
-        <v>83.08087388801675</v>
-      </c>
-      <c r="F4" s="4">
-        <v>74.266399931165</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1300</v>
-      </c>
-      <c r="H4" s="5">
-        <v>787</v>
-      </c>
-      <c r="I4" s="5">
-        <v>34</v>
-      </c>
-      <c r="J4" s="5">
-        <v>479</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>479</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.9793543063116789</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.9298872780254815</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.8240731488270691</v>
-      </c>
-      <c r="E5" s="4">
-        <v>83.52000323939099</v>
-      </c>
-      <c r="F5" s="4">
-        <v>75.89057561876398</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1260</v>
-      </c>
-      <c r="H5" s="5">
-        <v>842</v>
-      </c>
-      <c r="I5" s="5">
-        <v>10</v>
-      </c>
-      <c r="J5" s="5">
-        <v>408</v>
-      </c>
-      <c r="K5" s="5">
-        <v>3</v>
-      </c>
-      <c r="L5" s="5">
-        <v>403</v>
-      </c>
-      <c r="M5" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="4">
-        <v>1.344256027209443</v>
-      </c>
-      <c r="C6" s="4">
-        <v>1.374319954966815</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1.297535525345494</v>
-      </c>
-      <c r="E6" s="4">
-        <v>83.35059146811423</v>
-      </c>
-      <c r="F6" s="4">
-        <v>77.69055884330241</v>
-      </c>
-      <c r="G6" s="5">
-        <v>1015</v>
-      </c>
-      <c r="H6" s="5">
-        <v>696</v>
-      </c>
-      <c r="I6" s="5">
-        <v>18</v>
-      </c>
-      <c r="J6" s="5">
-        <v>301</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>301</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="4">
-        <v>1.288931432471761</v>
-      </c>
-      <c r="C7" s="4">
-        <v>1.238176652071127</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.8988287586669055</v>
-      </c>
-      <c r="E7" s="4">
-        <v>81.81182188869568</v>
-      </c>
-      <c r="F7" s="4">
-        <v>73.59568690790286</v>
-      </c>
-      <c r="G7" s="5">
-        <v>669</v>
-      </c>
-      <c r="H7" s="5">
-        <v>361</v>
-      </c>
-      <c r="I7" s="5">
-        <v>18</v>
-      </c>
-      <c r="J7" s="5">
-        <v>290</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>290</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="4">
-        <v>0.5801403259429982</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0.4448652452911565</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0.3928387852925546</v>
-      </c>
-      <c r="E8" s="4">
-        <v>83.54613964544927</v>
-      </c>
-      <c r="F8" s="4">
-        <v>73.78668612725865</v>
-      </c>
-      <c r="G8" s="5">
-        <v>538</v>
-      </c>
-      <c r="H8" s="5">
-        <v>313</v>
-      </c>
-      <c r="I8" s="5">
-        <v>40</v>
-      </c>
-      <c r="J8" s="5">
-        <v>185</v>
-      </c>
-      <c r="K8" s="5">
-        <v>5</v>
-      </c>
-      <c r="L8" s="5">
-        <v>180</v>
-      </c>
-      <c r="M8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/ZhangDopant-dependent2025.xlsx
+++ b/public/downloads/ZhangDopant-dependent2025.xlsx
@@ -1620,22 +1620,22 @@
         <v>186</v>
       </c>
       <c r="N3" s="4">
-        <v>0.9819113485465572</v>
+        <v>0.9441629742026976</v>
       </c>
       <c r="O3" s="5">
         <v>2134</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6577432386678714</v>
+        <v>0.652386957213506</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5850542866169058</v>
+        <v>0.5813291693225382</v>
       </c>
       <c r="R3" s="5">
-        <v>2116</v>
+        <v>2112</v>
       </c>
       <c r="S3" s="5">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -1679,16 +1679,16 @@
         <v>274</v>
       </c>
       <c r="N4" s="4">
-        <v>1.725644560536028</v>
+        <v>1.747943766629664</v>
       </c>
       <c r="O4" s="5">
         <v>1046</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3428987287192891</v>
+        <v>0.3463181633275489</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2982080429397095</v>
+        <v>0.2978226386605893</v>
       </c>
       <c r="R4" s="5">
         <v>1046</v>
@@ -1738,16 +1738,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3360989651063747</v>
+        <v>-0.3158967294580179</v>
       </c>
       <c r="O5" s="5">
         <v>1027</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3077647989374864</v>
+        <v>0.3049505301462515</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3027406284166927</v>
+        <v>0.3018150639857882</v>
       </c>
       <c r="R5" s="5">
         <v>1027</v>
@@ -1797,16 +1797,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.6346994263359634</v>
+        <v>-0.5953541002663201</v>
       </c>
       <c r="O6" s="5">
         <v>976</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1767370994514929</v>
+        <v>0.1711794899860185</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1727991608346863</v>
+        <v>0.1671404132637359</v>
       </c>
       <c r="R6" s="5">
         <v>976</v>
@@ -1856,16 +1856,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.5273995345712378</v>
+        <v>-0.5442179113431393</v>
       </c>
       <c r="O7" s="5">
         <v>499</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2482929496641412</v>
+        <v>0.2453236391103891</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2334397182719874</v>
+        <v>0.2331821591983484</v>
       </c>
       <c r="R7" s="5">
         <v>499</v>
@@ -1915,16 +1915,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.05761231017444256</v>
+        <v>0.07760897376697895</v>
       </c>
       <c r="O8" s="5">
         <v>464</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2291088766084902</v>
+        <v>0.2288884267200291</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1704692913477198</v>
+        <v>0.1684408272775103</v>
       </c>
       <c r="R8" s="5">
         <v>464</v>
@@ -2097,22 +2097,22 @@
         <v>539</v>
       </c>
       <c r="N3" s="4">
-        <v>2.260122762536059</v>
+        <v>2.201433041945382</v>
       </c>
       <c r="O3" s="5">
         <v>969</v>
       </c>
       <c r="P3" s="4">
-        <v>1.303721110663094</v>
+        <v>1.316072858087573</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.8798321082706825</v>
+        <v>0.8745281243343823</v>
       </c>
       <c r="R3" s="5">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="S3" s="5">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -2156,16 +2156,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1123956590570702</v>
+        <v>0.163682874855918</v>
       </c>
       <c r="O4" s="5">
         <v>787</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2323634538590199</v>
+        <v>0.2353896763820029</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2025924505005597</v>
+        <v>0.1989359435048478</v>
       </c>
       <c r="R4" s="5">
         <v>787</v>
@@ -2215,16 +2215,16 @@
         <v>2</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.9325342989873711</v>
+        <v>-0.7931381846825882</v>
       </c>
       <c r="O5" s="5">
         <v>844</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3251050665335309</v>
+        <v>0.3372113753049747</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3124280655756538</v>
+        <v>0.309539281067378</v>
       </c>
       <c r="R5" s="5">
         <v>844</v>
@@ -2274,16 +2274,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.374319954966815</v>
+        <v>-1.39411310857613</v>
       </c>
       <c r="O6" s="5">
         <v>696</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1689538796812292</v>
+        <v>0.1714226493278499</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1544345146716327</v>
+        <v>0.1536800621392396</v>
       </c>
       <c r="R6" s="5">
         <v>696</v>
@@ -2333,16 +2333,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.238176652071127</v>
+        <v>-1.280277014504009</v>
       </c>
       <c r="O7" s="5">
         <v>361</v>
       </c>
       <c r="P7" s="4">
-        <v>0.3037485012452711</v>
+        <v>0.2995621246574451</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1774091987484568</v>
+        <v>0.1749228878059724</v>
       </c>
       <c r="R7" s="5">
         <v>361</v>
@@ -2392,16 +2392,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.4448652452911565</v>
+        <v>-0.3427991718883807</v>
       </c>
       <c r="O8" s="5">
         <v>313</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3564419319828487</v>
+        <v>0.3690049147604682</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2880654680695822</v>
+        <v>0.2751085613737713</v>
       </c>
       <c r="R8" s="5">
         <v>313</v>
@@ -2574,16 +2574,16 @@
         <v>572</v>
       </c>
       <c r="N3" s="4">
-        <v>1.340471347416091</v>
+        <v>1.292761158198573</v>
       </c>
       <c r="O3" s="5">
         <v>2543</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7126926836092849</v>
+        <v>0.7115984382559589</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6457208386041666</v>
+        <v>0.6446975640135646</v>
       </c>
       <c r="R3" s="5">
         <v>2505</v>
@@ -2633,16 +2633,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.7795331661404522</v>
+        <v>0.7792777740645191</v>
       </c>
       <c r="O4" s="5">
         <v>1282</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1076514511404432</v>
+        <v>0.1076489160882209</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1041603434002084</v>
+        <v>0.1041601633198825</v>
       </c>
       <c r="R4" s="5">
         <v>1282</v>
@@ -2692,16 +2692,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.04115628920041</v>
+        <v>-0.01723763021033164</v>
       </c>
       <c r="O5" s="5">
         <v>1158</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1358486702103686</v>
+        <v>0.1349263629726207</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1189852525546344</v>
+        <v>0.1173170862347122</v>
       </c>
       <c r="R5" s="5">
         <v>1158</v>
@@ -2751,16 +2751,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.2713114394641331</v>
+        <v>0.2588357261502665</v>
       </c>
       <c r="O6" s="5">
         <v>1008</v>
       </c>
       <c r="P6" s="4">
-        <v>0.12192128376442</v>
+        <v>0.120993056468253</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1169676374100118</v>
+        <v>0.1161196009889677</v>
       </c>
       <c r="R6" s="5">
         <v>1008</v>
@@ -2810,16 +2810,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.1069990296538559</v>
+        <v>-0.1060688000874279</v>
       </c>
       <c r="O7" s="5">
         <v>608</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1545957607683498</v>
+        <v>0.1546533602481908</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1406224868223317</v>
+        <v>0.1406170159695758</v>
       </c>
       <c r="R7" s="5">
         <v>608</v>
@@ -2869,16 +2869,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.2952828775998159</v>
+        <v>0.3316214048278661</v>
       </c>
       <c r="O8" s="5">
         <v>514</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1676316154865241</v>
+        <v>0.1656667919233345</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.156513082652433</v>
+        <v>0.1527597757838159</v>
       </c>
       <c r="R8" s="5">
         <v>514</v>
@@ -3051,16 +3051,16 @@
         <v>23</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.05763792853148651</v>
+        <v>-0.03059020724850825</v>
       </c>
       <c r="O3" s="5">
         <v>1688</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7882413285243748</v>
+        <v>0.7949029576147252</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5815470782861492</v>
+        <v>0.5811648572405266</v>
       </c>
       <c r="R3" s="5">
         <v>1669</v>
@@ -3110,16 +3110,16 @@
         <v>110</v>
       </c>
       <c r="N4" s="4">
-        <v>1.937136505082173</v>
+        <v>1.840922093007634</v>
       </c>
       <c r="O4" s="5">
         <v>315</v>
       </c>
       <c r="P4" s="4">
-        <v>0.7508733222117771</v>
+        <v>0.802065455969074</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2666675621592036</v>
+        <v>0.2505787303836768</v>
       </c>
       <c r="R4" s="5">
         <v>315</v>
@@ -3169,16 +3169,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1018303467243184</v>
+        <v>-0.03996745304255001</v>
       </c>
       <c r="O5" s="5">
         <v>880</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2833188556365575</v>
+        <v>0.2809349598811097</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2016130586078355</v>
+        <v>0.1888434801693991</v>
       </c>
       <c r="R5" s="5">
         <v>880</v>
@@ -3228,16 +3228,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.1588468032715709</v>
+        <v>-0.1500758180782213</v>
       </c>
       <c r="O6" s="5">
         <v>811</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1060678523990335</v>
+        <v>0.1062110759309143</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1037889844910423</v>
+        <v>0.1035311277016239</v>
       </c>
       <c r="R6" s="5">
         <v>811</v>
@@ -3287,16 +3287,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.03038422267104736</v>
+        <v>-0.01013775672385009</v>
       </c>
       <c r="O7" s="5">
         <v>598</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2049328135928202</v>
+        <v>0.201125335071562</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.194754796769448</v>
+        <v>0.1919512902308882</v>
       </c>
       <c r="R7" s="5">
         <v>598</v>
@@ -3346,16 +3346,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.1791329848749302</v>
+        <v>-0.1676252377745167</v>
       </c>
       <c r="O8" s="5">
         <v>508</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2134601708896071</v>
+        <v>0.213499246153312</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1894743557397139</v>
+        <v>0.1889720655063739</v>
       </c>
       <c r="R8" s="5">
         <v>508</v>
@@ -3528,16 +3528,16 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3534800899030155</v>
+        <v>0.3252885716264586</v>
       </c>
       <c r="O3" s="5">
         <v>2738</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4897177643666333</v>
+        <v>0.4884435430111467</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4614282593230028</v>
+        <v>0.4609001713283734</v>
       </c>
       <c r="R3" s="5">
         <v>2738</v>
@@ -3587,22 +3587,22 @@
         <v>319</v>
       </c>
       <c r="N4" s="4">
-        <v>2.164181263319821</v>
+        <v>2.06188635031832</v>
       </c>
       <c r="O4" s="5">
         <v>628</v>
       </c>
       <c r="P4" s="4">
-        <v>0.8964630067182358</v>
+        <v>0.9194074354308817</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6026177890816858</v>
+        <v>0.5922747040361802</v>
       </c>
       <c r="R4" s="5">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="S4" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -3646,16 +3646,16 @@
         <v>14</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1041533110146466</v>
+        <v>-0.1647308069835844</v>
       </c>
       <c r="O5" s="5">
         <v>439</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4867380587164908</v>
+        <v>0.5020141498359211</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1756163186679031</v>
+        <v>0.1570518394642607</v>
       </c>
       <c r="R5" s="5">
         <v>425</v>
@@ -3705,16 +3705,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.05283755987624283</v>
+        <v>-0.0357368325802554</v>
       </c>
       <c r="O6" s="5">
         <v>1010</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1125907659502703</v>
+        <v>0.1119602159948318</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1114731189581876</v>
+        <v>0.1107547904024946</v>
       </c>
       <c r="R6" s="5">
         <v>1010</v>
@@ -3764,16 +3764,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.08428179642163802</v>
+        <v>-0.09846144401933543</v>
       </c>
       <c r="O7" s="5">
         <v>591</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1902665180964928</v>
+        <v>0.1902256758403327</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1519777999693841</v>
+        <v>0.1515956704672879</v>
       </c>
       <c r="R7" s="5">
         <v>591</v>
@@ -3823,16 +3823,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.02337691061890905</v>
+        <v>0.01042946396369526</v>
       </c>
       <c r="O8" s="5">
         <v>522</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1109844759994347</v>
+        <v>0.1059073347722695</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.09651358086112208</v>
+        <v>0.09050366041053563</v>
       </c>
       <c r="R8" s="5">
         <v>522</v>
@@ -4005,22 +4005,22 @@
         <v>538</v>
       </c>
       <c r="N3" s="4">
-        <v>1.118697946459242</v>
+        <v>1.077994327749934</v>
       </c>
       <c r="O3" s="5">
         <v>2599</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8153886011401899</v>
+        <v>0.8174390780445591</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.7570084175376214</v>
+        <v>0.7562143219517095</v>
       </c>
       <c r="R3" s="5">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="S3" s="5">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -4064,16 +4064,16 @@
         <v>276</v>
       </c>
       <c r="N4" s="4">
-        <v>1.901171529572975</v>
+        <v>1.912866227336508</v>
       </c>
       <c r="O4" s="5">
         <v>803</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2411645845076773</v>
+        <v>0.244823563500979</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1783692025888824</v>
+        <v>0.1779736465307847</v>
       </c>
       <c r="R4" s="5">
         <v>803</v>
@@ -4123,16 +4123,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4539332579838726</v>
+        <v>0.4549577559280351</v>
       </c>
       <c r="O5" s="5">
         <v>1096</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2808264305107054</v>
+        <v>0.2809199878742449</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2786843037414828</v>
+        <v>0.2786834283003669</v>
       </c>
       <c r="R5" s="5">
         <v>1096</v>
@@ -4182,16 +4182,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.1002998381523428</v>
+        <v>0.1234390349850258</v>
       </c>
       <c r="O6" s="5">
         <v>1011</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1008274104985462</v>
+        <v>0.09720335826560947</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1007060590758933</v>
+        <v>0.09702189348727201</v>
       </c>
       <c r="R6" s="5">
         <v>1011</v>
@@ -4241,16 +4241,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.1308045465188028</v>
+        <v>0.1014642329957383</v>
       </c>
       <c r="O7" s="5">
         <v>600</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2267887489929764</v>
+        <v>0.2257834010003576</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1812167371537654</v>
+        <v>0.1800278572961341</v>
       </c>
       <c r="R7" s="5">
         <v>600</v>
@@ -4300,16 +4300,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.2091117579193037</v>
+        <v>0.1892062911416343</v>
       </c>
       <c r="O8" s="5">
         <v>529</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1367591073223806</v>
+        <v>0.1354648637022355</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1266207241386377</v>
+        <v>0.1256431175854448</v>
       </c>
       <c r="R8" s="5">
         <v>529</v>
@@ -4482,22 +4482,22 @@
         <v>1733</v>
       </c>
       <c r="N3" s="4">
-        <v>-2.481246926873636</v>
+        <v>-2.567897111772368</v>
       </c>
       <c r="O3" s="5">
         <v>2301</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7670972158662838</v>
+        <v>0.7478803258120079</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6161763011326012</v>
+        <v>0.60846025803093</v>
       </c>
       <c r="R3" s="5">
-        <v>2285</v>
+        <v>2279</v>
       </c>
       <c r="S3" s="5">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -4594,16 +4594,16 @@
         <v>12</v>
       </c>
       <c r="N5" s="4">
-        <v>0.7078335553130313</v>
+        <v>0.5012641728392282</v>
       </c>
       <c r="O5" s="5">
         <v>113</v>
       </c>
       <c r="P5" s="4">
-        <v>0.8834608908113242</v>
+        <v>0.9963336391431165</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.339943618951194</v>
+        <v>0.2588096690856406</v>
       </c>
       <c r="R5" s="5">
         <v>101</v>
@@ -4653,16 +4653,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.4757829290814142</v>
+        <v>-0.464651271584934</v>
       </c>
       <c r="O6" s="5">
         <v>1005</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1022224737137491</v>
+        <v>0.101820808193637</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1016983906616663</v>
+        <v>0.1011819657085533</v>
       </c>
       <c r="R6" s="5">
         <v>1005</v>
@@ -4712,16 +4712,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.07382133599858602</v>
+        <v>-0.1079990086244607</v>
       </c>
       <c r="O7" s="5">
         <v>605</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2870047423268561</v>
+        <v>0.2847802803181443</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2562259947680011</v>
+        <v>0.2554468914463358</v>
       </c>
       <c r="R7" s="5">
         <v>605</v>
@@ -4771,16 +4771,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.2195908009011196</v>
+        <v>-0.2106262308550497</v>
       </c>
       <c r="O8" s="5">
         <v>476</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1698251254429213</v>
+        <v>0.1706126431585512</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1031866750699875</v>
+        <v>0.1029844470622917</v>
       </c>
       <c r="R8" s="5">
         <v>476</v>
@@ -4953,16 +4953,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.4947285959199219</v>
+        <v>0.5070185921434813</v>
       </c>
       <c r="O3" s="5">
         <v>163</v>
       </c>
       <c r="P3" s="4">
-        <v>2.409049882596162</v>
+        <v>2.397510695998795</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1147080497348605</v>
+        <v>0.1142713406701255</v>
       </c>
       <c r="R3" s="5">
         <v>163</v>
@@ -5012,16 +5012,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.7503207131464761</v>
+        <v>0.7447593872361722</v>
       </c>
       <c r="O4" s="5">
         <v>1237</v>
       </c>
       <c r="P4" s="4">
-        <v>0.06942382153160326</v>
+        <v>0.06930705814652692</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06554026005108625</v>
+        <v>0.06535164997123465</v>
       </c>
       <c r="R4" s="5">
         <v>1237</v>
@@ -5071,16 +5071,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.08326877389428296</v>
+        <v>0.08993560343333407</v>
       </c>
       <c r="O5" s="5">
         <v>1185</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1117159937894823</v>
+        <v>0.1118982589819631</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.08774269289760581</v>
+        <v>0.0875257946580911</v>
       </c>
       <c r="R5" s="5">
         <v>1185</v>
@@ -5130,16 +5130,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.3669918589589638</v>
+        <v>0.3661070777626492</v>
       </c>
       <c r="O6" s="5">
         <v>1015</v>
       </c>
       <c r="P6" s="4">
-        <v>0.04662348765435286</v>
+        <v>0.04661272125175201</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.04455373094265427</v>
+        <v>0.04454382648758174</v>
       </c>
       <c r="R6" s="5">
         <v>1014</v>
@@ -5189,16 +5189,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.1852920584706903</v>
+        <v>0.1650736414484868</v>
       </c>
       <c r="O7" s="5">
         <v>636</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1386281125991836</v>
+        <v>0.1380098103780668</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1337772494741122</v>
+        <v>0.1329679157146181</v>
       </c>
       <c r="R7" s="5">
         <v>636</v>
@@ -5248,16 +5248,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.1643482298759468</v>
+        <v>0.1814786031974873</v>
       </c>
       <c r="O8" s="5">
         <v>538</v>
       </c>
       <c r="P8" s="4">
-        <v>0.07004150844253584</v>
+        <v>0.06943258445278261</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.07004150844253584</v>
+        <v>0.06943258445278261</v>
       </c>
       <c r="R8" s="5">
         <v>538</v>
@@ -5430,16 +5430,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.02406139210791815</v>
+        <v>-0.01911836997311411</v>
       </c>
       <c r="O3" s="5">
         <v>3238</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1953917440146855</v>
+        <v>0.195596816691691</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1575311146566742</v>
+        <v>0.157480318725695</v>
       </c>
       <c r="R3" s="5">
         <v>3238</v>
@@ -5489,16 +5489,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.9442397940292493</v>
+        <v>0.9402438202408883</v>
       </c>
       <c r="O4" s="5">
         <v>1232</v>
       </c>
       <c r="P4" s="4">
-        <v>0.05519194154958425</v>
+        <v>0.05521983683773035</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.05019900923391741</v>
+        <v>0.05008573084747428</v>
       </c>
       <c r="R4" s="5">
         <v>1232</v>
@@ -5548,16 +5548,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2349149395955698</v>
+        <v>-0.2228600108053911</v>
       </c>
       <c r="O5" s="5">
         <v>1206</v>
       </c>
       <c r="P5" s="4">
-        <v>0.09839540306392432</v>
+        <v>0.09836567157193328</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.08421225851056233</v>
+        <v>0.08364142282683233</v>
       </c>
       <c r="R5" s="5">
         <v>1206</v>
@@ -5607,16 +5607,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.2855143406149649</v>
+        <v>-0.2949270267369819</v>
       </c>
       <c r="O6" s="5">
         <v>1011</v>
       </c>
       <c r="P6" s="4">
-        <v>0.06718182122968165</v>
+        <v>0.06659865346273512</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.06692307035695796</v>
+        <v>0.06637483639161408</v>
       </c>
       <c r="R6" s="5">
         <v>1011</v>
@@ -5666,16 +5666,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.2099001125602958</v>
+        <v>-0.2354818992624246</v>
       </c>
       <c r="O7" s="5">
         <v>644</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1234517403621946</v>
+        <v>0.123194791379683</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1203799960571975</v>
+        <v>0.1192788836502954</v>
       </c>
       <c r="R7" s="5">
         <v>644</v>
@@ -5725,16 +5725,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.05245341512409068</v>
+        <v>-0.04682461603752031</v>
       </c>
       <c r="O8" s="5">
         <v>534</v>
       </c>
       <c r="P8" s="4">
-        <v>0.05841384024738318</v>
+        <v>0.0582682437041054</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.05492097113514113</v>
+        <v>0.0547321206920143</v>
       </c>
       <c r="R8" s="5">
         <v>534</v>
@@ -5907,16 +5907,16 @@
         <v>7</v>
       </c>
       <c r="N3" s="4">
-        <v>0.08366530479387449</v>
+        <v>0.060234589868287</v>
       </c>
       <c r="O3" s="5">
         <v>2735</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4455541591892289</v>
+        <v>0.4431785984021169</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3733592419057173</v>
+        <v>0.3728098434827347</v>
       </c>
       <c r="R3" s="5">
         <v>2729</v>
@@ -5966,16 +5966,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.7109741981742077</v>
+        <v>0.7184077122100971</v>
       </c>
       <c r="O4" s="5">
         <v>1154</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1480726366312545</v>
+        <v>0.1486523623111866</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1093137109403517</v>
+        <v>0.1091950613568032</v>
       </c>
       <c r="R4" s="5">
         <v>1154</v>
@@ -6025,16 +6025,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.08029372216439548</v>
+        <v>0.09373633448171859</v>
       </c>
       <c r="O5" s="5">
         <v>1065</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1380294995840084</v>
+        <v>0.1394003223341176</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1012863376748737</v>
+        <v>0.1005730544696463</v>
       </c>
       <c r="R5" s="5">
         <v>1065</v>
@@ -6084,16 +6084,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.1808707514646403</v>
+        <v>0.1805850714398005</v>
       </c>
       <c r="O6" s="5">
         <v>1012</v>
       </c>
       <c r="P6" s="4">
-        <v>0.07150149319150419</v>
+        <v>0.07150000163958956</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.07136287696988999</v>
+        <v>0.07136222787392274</v>
       </c>
       <c r="R6" s="5">
         <v>1012</v>
@@ -6143,16 +6143,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.3435723246318842</v>
+        <v>0.3314475148908969</v>
       </c>
       <c r="O7" s="5">
         <v>575</v>
       </c>
       <c r="P7" s="4">
-        <v>0.153242945396386</v>
+        <v>0.1530019176707981</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1519064409343589</v>
+        <v>0.1515306237187231</v>
       </c>
       <c r="R7" s="5">
         <v>575</v>
@@ -6202,16 +6202,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.1557751628083957</v>
+        <v>0.1753995510015702</v>
       </c>
       <c r="O8" s="5">
         <v>503</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1425538586703055</v>
+        <v>0.1415553979375706</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1159361756604366</v>
+        <v>0.1144390779579788</v>
       </c>
       <c r="R8" s="5">
         <v>503</v>
@@ -6330,13 +6330,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="3">
-        <v>54.642166344294</v>
+        <v>54.54545454545454</v>
       </c>
       <c r="C3" s="3">
         <v>17.46856866537718</v>
       </c>
       <c r="D3" s="3">
-        <v>27.88926499032882</v>
+        <v>27.98597678916828</v>
       </c>
       <c r="E3" s="3">
         <v>10.94052224371373</v>
@@ -6345,16 +6345,16 @@
         <v>16.12669245647969</v>
       </c>
       <c r="G3" s="3">
-        <v>0.8220502901353964</v>
+        <v>0.918762088974855</v>
       </c>
       <c r="H3" s="4">
-        <v>1.553629048810329</v>
+        <v>1.554662650930437</v>
       </c>
       <c r="I3" s="4">
-        <v>0.4765174690013938</v>
+        <v>0.4725183635556532</v>
       </c>
       <c r="J3" s="4">
-        <v>6.595583512950965</v>
+        <v>6.602431618473843</v>
       </c>
       <c r="K3" s="4">
         <v>88.95262190949883</v>
@@ -6398,13 +6398,13 @@
         <v>0.0120889748549323</v>
       </c>
       <c r="H4" s="4">
-        <v>0.5128732537149608</v>
+        <v>0.5065340610950179</v>
       </c>
       <c r="I4" s="4">
-        <v>0.2992183654592619</v>
+        <v>0.2947243433266206</v>
       </c>
       <c r="J4" s="4">
-        <v>0.4072564251273192</v>
+        <v>0.4240729801142351</v>
       </c>
       <c r="K4" s="4">
         <v>84.03796431532005</v>
@@ -6430,13 +6430,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="3">
-        <v>71.55464216634429</v>
+        <v>71.39748549323018</v>
       </c>
       <c r="C5" s="3">
         <v>13.91441005802708</v>
       </c>
       <c r="D5" s="3">
-        <v>14.53094777562863</v>
+        <v>14.68810444874275</v>
       </c>
       <c r="E5" s="3">
         <v>0.5440038684719536</v>
@@ -6445,16 +6445,16 @@
         <v>12.45164410058027</v>
       </c>
       <c r="G5" s="3">
-        <v>1.535299806576402</v>
+        <v>1.692456479690522</v>
       </c>
       <c r="H5" s="4">
-        <v>0.5695836188461817</v>
+        <v>0.5664620974507857</v>
       </c>
       <c r="I5" s="4">
-        <v>0.4148447884525079</v>
+        <v>0.4064249637275653</v>
       </c>
       <c r="J5" s="4">
-        <v>0.7049243714978332</v>
+        <v>0.7222845040172772</v>
       </c>
       <c r="K5" s="4">
         <v>80.66818313398859</v>
@@ -6480,13 +6480,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="3">
-        <v>46.01063829787234</v>
+        <v>45.96228239845261</v>
       </c>
       <c r="C6" s="3">
         <v>14.96615087040619</v>
       </c>
       <c r="D6" s="3">
-        <v>39.02321083172147</v>
+        <v>39.0715667311412</v>
       </c>
       <c r="E6" s="3">
         <v>0.2901353965183753</v>
@@ -6495,16 +6495,16 @@
         <v>37.89893617021276</v>
       </c>
       <c r="G6" s="3">
-        <v>0.8341392649903289</v>
+        <v>0.8824951644100579</v>
       </c>
       <c r="H6" s="4">
-        <v>0.5896877543344705</v>
+        <v>0.5964753082937625</v>
       </c>
       <c r="I6" s="4">
-        <v>0.3934116590106763</v>
+        <v>0.3860173363968035</v>
       </c>
       <c r="J6" s="4">
-        <v>0.8459467720802533</v>
+        <v>0.8911913517738606</v>
       </c>
       <c r="K6" s="4">
         <v>73.84955311911992</v>
@@ -6548,13 +6548,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.1331244190821007</v>
+        <v>0.1322093999496127</v>
       </c>
       <c r="I7" s="4">
-        <v>0.1083673926442958</v>
+        <v>0.1074109438665687</v>
       </c>
       <c r="J7" s="4">
-        <v>0.1134765612977554</v>
+        <v>0.1125665257204113</v>
       </c>
       <c r="K7" s="4">
         <v>96.86285345859815</v>
@@ -6580,13 +6580,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="3">
-        <v>74.08123791102514</v>
+        <v>74.03288201160542</v>
       </c>
       <c r="C8" s="3">
         <v>15.63104448742747</v>
       </c>
       <c r="D8" s="3">
-        <v>10.28771760154739</v>
+        <v>10.33607350096712</v>
       </c>
       <c r="E8" s="3">
         <v>0.1813346228239845</v>
@@ -6595,16 +6595,16 @@
         <v>9.888781431334623</v>
       </c>
       <c r="G8" s="3">
-        <v>0.2176015473887814</v>
+        <v>0.2659574468085106</v>
       </c>
       <c r="H8" s="4">
-        <v>0.4349410797668186</v>
+        <v>0.4318535337840017</v>
       </c>
       <c r="I8" s="4">
-        <v>0.3630958323038463</v>
+        <v>0.3603685893213142</v>
       </c>
       <c r="J8" s="4">
-        <v>0.5235608809339586</v>
+        <v>0.5244371905671477</v>
       </c>
       <c r="K8" s="4">
         <v>91.05157222463453</v>
@@ -6630,13 +6630,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>46.31286266924565</v>
+        <v>46.28868471953578</v>
       </c>
       <c r="C9" s="3">
         <v>7.990812379110252</v>
       </c>
       <c r="D9" s="3">
-        <v>45.6963249516441</v>
+        <v>45.72050290135397</v>
       </c>
       <c r="E9" s="3">
         <v>0.5681818181818182</v>
@@ -6645,16 +6645,16 @@
         <v>43.44777562862669</v>
       </c>
       <c r="G9" s="3">
-        <v>1.68036750483559</v>
+        <v>1.704545454545454</v>
       </c>
       <c r="H9" s="4">
-        <v>0.7045639802562231</v>
+        <v>0.7128763154631568</v>
       </c>
       <c r="I9" s="4">
-        <v>0.3693776638527504</v>
+        <v>0.3651450752585291</v>
       </c>
       <c r="J9" s="4">
-        <v>0.9925033604158195</v>
+        <v>1.000247712449488</v>
       </c>
       <c r="K9" s="4">
         <v>79.75043257148117</v>
@@ -6698,13 +6698,13 @@
         <v>0.4593810444874275</v>
       </c>
       <c r="H10" s="4">
-        <v>0.376665153874602</v>
+        <v>0.3758255732772674</v>
       </c>
       <c r="I10" s="4">
-        <v>0.3070952308666277</v>
+        <v>0.306065885703057</v>
       </c>
       <c r="J10" s="4">
-        <v>0.4161477512154155</v>
+        <v>0.4173898132646784</v>
       </c>
       <c r="K10" s="4">
         <v>89.24772447663777</v>
@@ -6748,13 +6748,13 @@
         <v>0.2296905222437138</v>
       </c>
       <c r="H11" s="4">
-        <v>0.5371953346161347</v>
+        <v>0.5474001631949492</v>
       </c>
       <c r="I11" s="4">
-        <v>0.319788967772593</v>
+        <v>0.3157973509215006</v>
       </c>
       <c r="J11" s="4">
-        <v>1.458949107525936</v>
+        <v>1.463888694272712</v>
       </c>
       <c r="K11" s="4">
         <v>88.62407317859473</v>
@@ -6780,13 +6780,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>71.36121856866538</v>
+        <v>71.33704061895551</v>
       </c>
       <c r="C12" s="3">
         <v>15.09912959381045</v>
       </c>
       <c r="D12" s="3">
-        <v>13.53965183752418</v>
+        <v>13.56382978723404</v>
       </c>
       <c r="E12" s="3">
         <v>0.6890715667311412</v>
@@ -6795,16 +6795,16 @@
         <v>12.54835589941973</v>
       </c>
       <c r="G12" s="3">
-        <v>0.3022243713733075</v>
+        <v>0.3264023210831721</v>
       </c>
       <c r="H12" s="4">
-        <v>0.4580614647594063</v>
+        <v>0.4630457207980811</v>
       </c>
       <c r="I12" s="4">
-        <v>0.3324800109203493</v>
+        <v>0.3290355760275605</v>
       </c>
       <c r="J12" s="4">
-        <v>1.243584896379664</v>
+        <v>1.270971014959596</v>
       </c>
       <c r="K12" s="4">
         <v>88.57734559007346</v>
@@ -6830,13 +6830,13 @@
         <v>27</v>
       </c>
       <c r="B13" s="3">
-        <v>79.53336557059961</v>
+        <v>79.54545454545455</v>
       </c>
       <c r="C13" s="3">
         <v>9.973404255319149</v>
       </c>
       <c r="D13" s="3">
-        <v>10.49323017408124</v>
+        <v>10.48114119922631</v>
       </c>
       <c r="E13" s="3">
         <v>0.5077369439071566</v>
@@ -6845,16 +6845,16 @@
         <v>9.272243713733076</v>
       </c>
       <c r="G13" s="3">
-        <v>0.7132495164410058</v>
+        <v>0.7011605415860735</v>
       </c>
       <c r="H13" s="4">
-        <v>0.4643011816676134</v>
+        <v>0.465145406217235</v>
       </c>
       <c r="I13" s="4">
-        <v>0.4026441827348264</v>
+        <v>0.4015898975010226</v>
       </c>
       <c r="J13" s="4">
-        <v>0.5389741241323918</v>
+        <v>0.5417504825345024</v>
       </c>
       <c r="K13" s="4">
         <v>86.69234957038906</v>
@@ -6880,13 +6880,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="3">
-        <v>54.06189555125726</v>
+        <v>53.98936170212766</v>
       </c>
       <c r="C14" s="3">
         <v>12.52417794970986</v>
       </c>
       <c r="D14" s="3">
-        <v>33.41392649903288</v>
+        <v>33.48646034816248</v>
       </c>
       <c r="E14" s="3">
         <v>2.381528046421664</v>
@@ -6895,16 +6895,16 @@
         <v>30.68181818181818</v>
       </c>
       <c r="G14" s="3">
-        <v>0.3505802707930368</v>
+        <v>0.4231141199226305</v>
       </c>
       <c r="H14" s="4">
-        <v>1.054561822527934</v>
+        <v>1.063469045152801</v>
       </c>
       <c r="I14" s="4">
-        <v>0.3910191458821542</v>
+        <v>0.3847009731961306</v>
       </c>
       <c r="J14" s="4">
-        <v>2.180793732473049</v>
+        <v>2.212937859947775</v>
       </c>
       <c r="K14" s="4">
         <v>85.87513487019545</v>
@@ -6948,13 +6948,13 @@
         <v>0.0120889748549323</v>
       </c>
       <c r="H15" s="4">
-        <v>1.065805680520617</v>
+        <v>1.060855720090982</v>
       </c>
       <c r="I15" s="4">
-        <v>0.07787302540479989</v>
+        <v>0.07757679679488534</v>
       </c>
       <c r="J15" s="4">
-        <v>0.5059381596407519</v>
+        <v>0.5018268640548957</v>
       </c>
       <c r="K15" s="4">
         <v>95.71748065764029</v>
@@ -6998,13 +6998,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.1281250395780686</v>
+        <v>0.1281096093005537</v>
       </c>
       <c r="I16" s="4">
-        <v>0.1078197905373326</v>
+        <v>0.1075201476769608</v>
       </c>
       <c r="J16" s="4">
-        <v>0.1754669240497785</v>
+        <v>0.1773837630449182</v>
       </c>
       <c r="K16" s="4">
         <v>89.95696489427473</v>
@@ -7048,13 +7048,13 @@
         <v>0.07253384912959382</v>
       </c>
       <c r="H17" s="4">
-        <v>0.2627155627044335</v>
+        <v>0.261928599401025</v>
       </c>
       <c r="I17" s="4">
-        <v>0.2089793513210562</v>
+        <v>0.2085011375589437</v>
       </c>
       <c r="J17" s="4">
-        <v>0.2791479264438044</v>
+        <v>0.2792656617319106</v>
       </c>
       <c r="K17" s="4">
         <v>92.25240216976553</v>
@@ -7098,13 +7098,13 @@
         <v>0.09671179883945842</v>
       </c>
       <c r="H18" s="4">
-        <v>0.3142637197174933</v>
+        <v>0.3142997641327464</v>
       </c>
       <c r="I18" s="4">
-        <v>0.2834355298932507</v>
+        <v>0.2829561042067723</v>
       </c>
       <c r="J18" s="4">
-        <v>0.3181071164546737</v>
+        <v>0.3161766196412641</v>
       </c>
       <c r="K18" s="4">
         <v>90.66779250384869</v>
@@ -7291,16 +7291,16 @@
         <v>166</v>
       </c>
       <c r="N3" s="4">
-        <v>1.016763890508596</v>
+        <v>1.032736285025862</v>
       </c>
       <c r="O3" s="5">
         <v>2693</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5296837558775771</v>
+        <v>0.5302397149707891</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5162387356018742</v>
+        <v>0.5160713016740581</v>
       </c>
       <c r="R3" s="5">
         <v>2685</v>
@@ -7350,16 +7350,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4849976781787187</v>
+        <v>0.5096263032847501</v>
       </c>
       <c r="O4" s="5">
         <v>1259</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1744290408941523</v>
+        <v>0.1736733970932861</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.173219810382425</v>
+        <v>0.1719856027652871</v>
       </c>
       <c r="R4" s="5">
         <v>1259</v>
@@ -7409,16 +7409,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.0332075817416683</v>
+        <v>-0.02850462752076055</v>
       </c>
       <c r="O5" s="5">
         <v>1185</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1470990085152149</v>
+        <v>0.1472571466982283</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1278628783994427</v>
+        <v>0.1277567312504991</v>
       </c>
       <c r="R5" s="5">
         <v>1185</v>
@@ -7468,16 +7468,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.08634435159529383</v>
+        <v>-0.09179655977129642</v>
       </c>
       <c r="O6" s="5">
         <v>1011</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1731168995311282</v>
+        <v>0.1730530269871378</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.173092831521953</v>
+        <v>0.17301792049475</v>
       </c>
       <c r="R6" s="5">
         <v>1011</v>
@@ -7527,16 +7527,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.06724703260005652</v>
+        <v>-0.06321825734443109</v>
       </c>
       <c r="O7" s="5">
         <v>632</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1399964199342545</v>
+        <v>0.1401553937997714</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1165962850691267</v>
+        <v>0.1165414533952089</v>
       </c>
       <c r="R7" s="5">
         <v>632</v>
@@ -7586,16 +7586,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.06790303323325575</v>
+        <v>0.1005530037641185</v>
       </c>
       <c r="O8" s="5">
         <v>527</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1292182521165063</v>
+        <v>0.1275443155260083</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1222162629840792</v>
+        <v>0.1198258881045205</v>
       </c>
       <c r="R8" s="5">
         <v>527</v>
@@ -8508,13 +8508,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="5">
-        <v>4520</v>
+        <v>4512</v>
       </c>
       <c r="C3" s="5">
         <v>1445</v>
       </c>
       <c r="D3" s="5">
-        <v>2307</v>
+        <v>2315</v>
       </c>
       <c r="E3" s="5">
         <v>905</v>
@@ -8523,7 +8523,7 @@
         <v>1334</v>
       </c>
       <c r="G3" s="5">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H3" s="5">
         <v>905</v>
@@ -8596,13 +8596,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="5">
-        <v>5919</v>
+        <v>5906</v>
       </c>
       <c r="C5" s="5">
         <v>1151</v>
       </c>
       <c r="D5" s="5">
-        <v>1202</v>
+        <v>1215</v>
       </c>
       <c r="E5" s="5">
         <v>45</v>
@@ -8611,7 +8611,7 @@
         <v>1030</v>
       </c>
       <c r="G5" s="5">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="H5" s="5">
         <v>45</v>
@@ -8640,13 +8640,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <v>3806</v>
+        <v>3802</v>
       </c>
       <c r="C6" s="5">
         <v>1238</v>
       </c>
       <c r="D6" s="5">
-        <v>3228</v>
+        <v>3232</v>
       </c>
       <c r="E6" s="5">
         <v>24</v>
@@ -8655,7 +8655,7 @@
         <v>3135</v>
       </c>
       <c r="G6" s="5">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H6" s="5">
         <v>24</v>
@@ -8728,13 +8728,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="5">
-        <v>6128</v>
+        <v>6124</v>
       </c>
       <c r="C8" s="5">
         <v>1293</v>
       </c>
       <c r="D8" s="5">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="E8" s="5">
         <v>15</v>
@@ -8743,7 +8743,7 @@
         <v>818</v>
       </c>
       <c r="G8" s="5">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H8" s="5">
         <v>15</v>
@@ -8772,13 +8772,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>3831</v>
+        <v>3829</v>
       </c>
       <c r="C9" s="5">
         <v>661</v>
       </c>
       <c r="D9" s="5">
-        <v>3780</v>
+        <v>3782</v>
       </c>
       <c r="E9" s="5">
         <v>47</v>
@@ -8787,7 +8787,7 @@
         <v>3594</v>
       </c>
       <c r="G9" s="5">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H9" s="5">
         <v>47</v>
@@ -8904,13 +8904,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>5903</v>
+        <v>5901</v>
       </c>
       <c r="C12" s="5">
         <v>1249</v>
       </c>
       <c r="D12" s="5">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="E12" s="5">
         <v>57</v>
@@ -8919,7 +8919,7 @@
         <v>1038</v>
       </c>
       <c r="G12" s="5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H12" s="5">
         <v>57</v>
@@ -8948,13 +8948,13 @@
         <v>27</v>
       </c>
       <c r="B13" s="5">
-        <v>6579</v>
+        <v>6580</v>
       </c>
       <c r="C13" s="5">
         <v>825</v>
       </c>
       <c r="D13" s="5">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="E13" s="5">
         <v>42</v>
@@ -8963,7 +8963,7 @@
         <v>767</v>
       </c>
       <c r="G13" s="5">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H13" s="5">
         <v>42</v>
@@ -8992,13 +8992,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="5">
-        <v>4472</v>
+        <v>4466</v>
       </c>
       <c r="C14" s="5">
         <v>1036</v>
       </c>
       <c r="D14" s="5">
-        <v>2764</v>
+        <v>2770</v>
       </c>
       <c r="E14" s="5">
         <v>197</v>
@@ -9007,7 +9007,7 @@
         <v>2538</v>
       </c>
       <c r="G14" s="5">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H14" s="5">
         <v>197</v>
@@ -9366,22 +9366,22 @@
         <v>385</v>
       </c>
       <c r="N3" s="4">
-        <v>0.9479253781350711</v>
+        <v>0.8873409210940579</v>
       </c>
       <c r="O3" s="5">
         <v>2531</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7946853260850163</v>
+        <v>0.7970859158035775</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.7459435568170002</v>
+        <v>0.7397086130415192</v>
       </c>
       <c r="R3" s="5">
-        <v>2463</v>
+        <v>2455</v>
       </c>
       <c r="S3" s="5">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -9531,16 +9531,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.5842797136229048</v>
+        <v>-0.5875167020303387</v>
       </c>
       <c r="O6" s="5">
         <v>1011</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1654131969162824</v>
+        <v>0.1653876896183305</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1654931407345905</v>
+        <v>0.1654803395933526</v>
       </c>
       <c r="R6" s="5">
         <v>1011</v>
@@ -9590,16 +9590,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.3593939146418442</v>
+        <v>-0.3776173574059385</v>
       </c>
       <c r="O7" s="5">
         <v>517</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1994982680708965</v>
+        <v>0.1998072294637546</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1849756045652493</v>
+        <v>0.183878010259641</v>
       </c>
       <c r="R7" s="5">
         <v>517</v>
@@ -9649,16 +9649,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.1416358040285098</v>
+        <v>-0.1424732212049911</v>
       </c>
       <c r="O8" s="5">
         <v>529</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1114377441982315</v>
+        <v>0.1114211890966537</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1014253811023138</v>
+        <v>0.1014227915180785</v>
       </c>
       <c r="R8" s="5">
         <v>529</v>
@@ -9831,16 +9831,16 @@
         <v>8</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.751817093973262</v>
+        <v>-0.7762416596522144</v>
       </c>
       <c r="O3" s="5">
         <v>1221</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8166344676950249</v>
+        <v>0.8084232328953244</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4352143445214753</v>
+        <v>0.4347525542941414</v>
       </c>
       <c r="R3" s="5">
         <v>1220</v>
@@ -9890,16 +9890,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4779520507839981</v>
+        <v>0.3849546159947455</v>
       </c>
       <c r="O4" s="5">
         <v>997</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2911926697603702</v>
+        <v>0.2851070971790938</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2665245382373198</v>
+        <v>0.2527191867550186</v>
       </c>
       <c r="R4" s="5">
         <v>997</v>
@@ -9949,16 +9949,16 @@
         <v>34</v>
       </c>
       <c r="N5" s="4">
-        <v>-1.477040555650098</v>
+        <v>-1.525390887966528</v>
       </c>
       <c r="O5" s="5">
         <v>470</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2832180902445739</v>
+        <v>0.2647403321373306</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2260394299862759</v>
+        <v>0.2215714051713278</v>
       </c>
       <c r="R5" s="5">
         <v>470</v>
@@ -10008,16 +10008,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.4008128083953016</v>
+        <v>-0.4061159920799469</v>
       </c>
       <c r="O6" s="5">
         <v>976</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2295752883988079</v>
+        <v>0.2294593276337713</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2250716892318951</v>
+        <v>0.2250217314566781</v>
       </c>
       <c r="R6" s="5">
         <v>976</v>
@@ -10067,16 +10067,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.136406884444126</v>
+        <v>-1.069801778784949</v>
       </c>
       <c r="O7" s="5">
         <v>433</v>
       </c>
       <c r="P7" s="4">
-        <v>0.5105877536042301</v>
+        <v>0.5247194335680582</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.4185847535913781</v>
+        <v>0.4145765229795056</v>
       </c>
       <c r="R7" s="5">
         <v>433</v>
@@ -10126,16 +10126,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.5928337898476563</v>
+        <v>-0.5418536151161875</v>
       </c>
       <c r="O8" s="5">
         <v>502</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1532079427357905</v>
+        <v>0.1496321694091791</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1433543433345275</v>
+        <v>0.1384700804777443</v>
       </c>
       <c r="R8" s="5">
         <v>502</v>
@@ -10308,22 +10308,22 @@
         <v>474</v>
       </c>
       <c r="N3" s="4">
-        <v>1.310281669241787</v>
+        <v>1.175396580816198</v>
       </c>
       <c r="O3" s="5">
         <v>1698</v>
       </c>
       <c r="P3" s="4">
-        <v>0.967751480212575</v>
+        <v>0.9714512657772294</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.8329146192916319</v>
+        <v>0.8126293098531209</v>
       </c>
       <c r="R3" s="5">
-        <v>1571</v>
+        <v>1558</v>
       </c>
       <c r="S3" s="5">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -10367,16 +10367,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4360050519184081</v>
+        <v>0.302279163376511</v>
       </c>
       <c r="O4" s="5">
         <v>1101</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3369712888137829</v>
+        <v>0.3129934388614787</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3049127242381223</v>
+        <v>0.298804212840956</v>
       </c>
       <c r="R4" s="5">
         <v>1101</v>
@@ -10426,16 +10426,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4450389279639529</v>
+        <v>-0.4810255028124857</v>
       </c>
       <c r="O5" s="5">
         <v>1225</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3730970025908129</v>
+        <v>0.3716616977186125</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3575160263912761</v>
+        <v>0.35671537911172</v>
       </c>
       <c r="R5" s="5">
         <v>1225</v>
@@ -10485,16 +10485,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.6945662180134372</v>
+        <v>-0.6761063813551118</v>
       </c>
       <c r="O6" s="5">
         <v>988</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1413821884771314</v>
+        <v>0.1407243685827127</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1352276166132494</v>
+        <v>0.1342341910909554</v>
       </c>
       <c r="R6" s="5">
         <v>988</v>
@@ -10544,16 +10544,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.4155674305653763</v>
+        <v>-0.4082117631249389</v>
       </c>
       <c r="O7" s="5">
         <v>572</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1713432011405112</v>
+        <v>0.170929918322281</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1655138918160258</v>
+        <v>0.1653661942434745</v>
       </c>
       <c r="R7" s="5">
         <v>572</v>
@@ -10603,16 +10603,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.1824044946025602</v>
+        <v>-0.04408365471311981</v>
       </c>
       <c r="O8" s="5">
         <v>462</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3119825419406986</v>
+        <v>0.3030427387285053</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.3138800062664451</v>
+        <v>0.3054042194133274</v>
       </c>
       <c r="R8" s="5">
         <v>462</v>
@@ -10785,22 +10785,22 @@
         <v>376</v>
       </c>
       <c r="N3" s="4">
-        <v>1.661851415947627</v>
+        <v>1.489456483356037</v>
       </c>
       <c r="O3" s="5">
         <v>1078</v>
       </c>
       <c r="P3" s="4">
-        <v>0.9336646200640316</v>
+        <v>0.9394437402895649</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.7912223317544755</v>
+        <v>0.7685405928040767</v>
       </c>
       <c r="R3" s="5">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="S3" s="5">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -10844,16 +10844,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1642673449767935</v>
+        <v>-0.1659390468683926</v>
       </c>
       <c r="O4" s="5">
         <v>827</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2547537685432583</v>
+        <v>0.2543218262937174</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1832291423578742</v>
+        <v>0.1832252045919341</v>
       </c>
       <c r="R4" s="5">
         <v>827</v>
@@ -10903,16 +10903,16 @@
         <v>2</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.6365731433972929</v>
+        <v>-0.5848823252920283</v>
       </c>
       <c r="O5" s="5">
         <v>369</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4657269221169018</v>
+        <v>0.494798274726385</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2564209718789762</v>
+        <v>0.2544073878531986</v>
       </c>
       <c r="R5" s="5">
         <v>368</v>
@@ -10962,16 +10962,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.8416015685477901</v>
+        <v>-0.8094636379122448</v>
       </c>
       <c r="O6" s="5">
         <v>813</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2634840054410612</v>
+        <v>0.2679560485087018</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2393829555059815</v>
+        <v>0.238524432097026</v>
       </c>
       <c r="R6" s="5">
         <v>813</v>
@@ -11021,16 +11021,16 @@
         <v>14</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.212999258774814</v>
+        <v>-1.280744026609909</v>
       </c>
       <c r="O7" s="5">
         <v>417</v>
       </c>
       <c r="P7" s="4">
-        <v>0.4252692823776592</v>
+        <v>0.4154082226639106</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.4268955579724044</v>
+        <v>0.4225870984314166</v>
       </c>
       <c r="R7" s="5">
         <v>417</v>
@@ -11080,16 +11080,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.3494381451147357</v>
+        <v>-0.3258559942523469</v>
       </c>
       <c r="O8" s="5">
         <v>371</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2778259171457356</v>
+        <v>0.2814821673975009</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.21472509498742</v>
+        <v>0.213470971297726</v>
       </c>
       <c r="R8" s="5">
         <v>371</v>
@@ -11262,16 +11262,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1923855028290324</v>
+        <v>-0.183377365700494</v>
       </c>
       <c r="O3" s="5">
         <v>3183</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1780017278864942</v>
+        <v>0.1783933636515259</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.138284630938787</v>
+        <v>0.1380812778427097</v>
       </c>
       <c r="R3" s="5">
         <v>3183</v>
@@ -11321,16 +11321,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.8691649302660104</v>
+        <v>0.8484036183535961</v>
       </c>
       <c r="O4" s="5">
         <v>1269</v>
       </c>
       <c r="P4" s="4">
-        <v>0.07265224155654214</v>
+        <v>0.07043253001368786</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06821051062798039</v>
+        <v>0.06575661036261624</v>
       </c>
       <c r="R4" s="5">
         <v>1269</v>
@@ -11380,16 +11380,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.02871901425934644</v>
+        <v>0.001675077048105322</v>
       </c>
       <c r="O5" s="5">
         <v>1168</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1583729775831024</v>
+        <v>0.1548645986128288</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1262864014173563</v>
+        <v>0.1245015979923283</v>
       </c>
       <c r="R5" s="5">
         <v>1168</v>
@@ -11439,16 +11439,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.1060807015136412</v>
+        <v>0.1036235661242699</v>
       </c>
       <c r="O6" s="5">
         <v>1013</v>
       </c>
       <c r="P6" s="4">
-        <v>0.07155580986101853</v>
+        <v>0.07151066129122625</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.0713980367447246</v>
+        <v>0.07135765024170346</v>
       </c>
       <c r="R6" s="5">
         <v>1013</v>
@@ -11498,16 +11498,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.02382147472023172</v>
+        <v>-0.05108604433445407</v>
       </c>
       <c r="O7" s="5">
         <v>640</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1169463679825334</v>
+        <v>0.1147828883228017</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.104735587769052</v>
+        <v>0.1024314745472165</v>
       </c>
       <c r="R7" s="5">
         <v>640</v>
@@ -11557,16 +11557,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.02605915424773427</v>
+        <v>0.01929688322920642</v>
       </c>
       <c r="O8" s="5">
         <v>531</v>
       </c>
       <c r="P8" s="4">
-        <v>0.0652695750107975</v>
+        <v>0.0650159116558798</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.0604906020356813</v>
+        <v>0.06029726958774706</v>
       </c>
       <c r="R8" s="5">
         <v>531</v>
